--- a/Excel/UnionQiangHuaConfig.xlsx
+++ b/Excel/UnionQiangHuaConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD37603-1DD6-4C15-B8CF-D561ACFC9F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A99A114-E89C-42A5-A26B-262C826266E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnionQiangHuaProto" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -579,7 +579,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1132,7 +1132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1270,7 +1270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="417">
   <si>
     <t>Id</t>
   </si>
@@ -2149,6 +2149,410 @@
   </si>
   <si>
     <t>231303;0.15</t>
+  </si>
+  <si>
+    <t>Attack Training Level 3</t>
+  </si>
+  <si>
+    <t>Attack Training Level 4</t>
+  </si>
+  <si>
+    <t>Life Training Level 3</t>
+  </si>
+  <si>
+    <t>Defense Training Level 0</t>
+  </si>
+  <si>
+    <t>Defense Training Level 1</t>
+  </si>
+  <si>
+    <t>Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>EquipSpaceName_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Training Level 1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Training Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Training Level 2</t>
+  </si>
+  <si>
+    <t>Attack Training Level 5</t>
+  </si>
+  <si>
+    <t>Attack Training Level 6</t>
+  </si>
+  <si>
+    <t>Attack Training Level 7</t>
+  </si>
+  <si>
+    <t>Attack Training Level 8</t>
+  </si>
+  <si>
+    <t>Attack Training Level 9</t>
+  </si>
+  <si>
+    <t>Attack Training Level 10</t>
+  </si>
+  <si>
+    <t>Attack Training Level 11</t>
+  </si>
+  <si>
+    <t>Attack Training Level 12</t>
+  </si>
+  <si>
+    <t>Attack Training Level 13</t>
+  </si>
+  <si>
+    <t>Attack Training Level 14</t>
+  </si>
+  <si>
+    <t>Attack Training Level 15</t>
+  </si>
+  <si>
+    <t>Life Training Level 0</t>
+  </si>
+  <si>
+    <t>Life Training Level 1</t>
+  </si>
+  <si>
+    <t>Life Training Level 2</t>
+  </si>
+  <si>
+    <t>Life Training Level 4</t>
+  </si>
+  <si>
+    <t>Life Training Level 5</t>
+  </si>
+  <si>
+    <t>Life Training Level 6</t>
+  </si>
+  <si>
+    <t>Life Training Level 7</t>
+  </si>
+  <si>
+    <t>Life Training Level 8</t>
+  </si>
+  <si>
+    <t>Life Training Level 9</t>
+  </si>
+  <si>
+    <t>Life Training Level 10</t>
+  </si>
+  <si>
+    <t>Life Training Level 11</t>
+  </si>
+  <si>
+    <t>Life Training Level 12</t>
+  </si>
+  <si>
+    <t>Life Training Level 13</t>
+  </si>
+  <si>
+    <t>Life Training Level 14</t>
+  </si>
+  <si>
+    <t>Life Training Level 15</t>
+  </si>
+  <si>
+    <t>Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>Defense Training Level 4</t>
+  </si>
+  <si>
+    <t>Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>Defense Training Level 9</t>
+  </si>
+  <si>
+    <t>Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>Defense Training Level 15</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 15</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 2</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 3</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 5</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 6</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 7</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 8</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 10</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 11</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 12</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 13</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 14</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Attack Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Attack Level 2</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 3</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 4</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Attack Level 5</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 6</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 7</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 8</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 9</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 10</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 11</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 12</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 13</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 14</t>
+  </si>
+  <si>
+    <t>Pet Attack Level 15</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Magic Level 1</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 2</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 3</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 4</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 5</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 6</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 7</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 8</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 9</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 10</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 11</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 12</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 13</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 14</t>
+  </si>
+  <si>
+    <t>Pet Magic Level 15</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 9</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Defense Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Defense Level 2</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 3</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 4</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 5</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 6</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 7</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 8</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 9</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 10</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 11</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 12</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Defense Level 13</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 14</t>
+  </si>
+  <si>
+    <t>Pet Defense Level 15</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 1</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 2</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 3</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 4</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 5</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 6</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 7</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 8</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 9</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 10</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 11</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 12</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 13</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 14</t>
+  </si>
+  <si>
+    <t>Pet Magic Defense Level 15</t>
   </si>
 </sst>
 </file>
@@ -2244,7 +2648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2338,11 +2742,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="12"/>
+      </left>
+      <right style="hair">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2367,6 +2782,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3525,21 +3943,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:ID133"/>
+  <dimension ref="C1:IE133"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
-    <col min="4" max="9" width="14.125" style="2" customWidth="1"/>
-    <col min="10" max="11" width="24.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.75" style="2" customWidth="1"/>
-    <col min="13" max="238" width="8.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="14.125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="24.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.75" style="2" customWidth="1"/>
+    <col min="14" max="239" width="8.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:238" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" spans="3:238" ht="13.5" customHeight="1">
+    <row r="1" spans="3:239" s="1" customFormat="1" ht="14.25"/>
+    <row r="2" spans="3:239" ht="13.5" customHeight="1">
       <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="E2" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -3547,71 +3970,77 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>19</v>
+      <c r="E5" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>19</v>
@@ -3620,4063 +4049,4450 @@
         <v>19</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C6" s="8">
         <v>10100</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" s="8">
         <v>10101</v>
       </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
       <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
         <v>1</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11">
         <v>100</v>
       </c>
-      <c r="J6" s="10"/>
       <c r="K6" s="10"/>
-      <c r="L6" s="10">
+      <c r="L6" s="10"/>
+      <c r="M6" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C7" s="8">
         <v>10101</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" s="8">
         <v>10102</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="10">
         <v>1</v>
       </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
       <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
         <v>0.8</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11">
         <v>220</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="10"/>
+      <c r="L7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="8" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C8" s="8">
         <v>10102</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F8" s="8">
         <v>10103</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="10">
         <v>2</v>
       </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
       <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
         <v>0.7</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="11">
         <v>375</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="10"/>
+      <c r="L8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID8"/>
-    </row>
-    <row r="9" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M8" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE8"/>
+    </row>
+    <row r="9" spans="3:239" ht="19.5" customHeight="1">
       <c r="C9" s="8">
         <v>10103</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F9" s="8">
         <v>10104</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="10">
         <v>3</v>
       </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
       <c r="H9" s="10">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
         <v>0.6</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="11">
         <v>560</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="10"/>
+      <c r="L9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID9"/>
-    </row>
-    <row r="10" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M9" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE9"/>
+    </row>
+    <row r="10" spans="3:239" ht="19.5" customHeight="1">
       <c r="C10" s="8">
         <v>10104</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F10" s="8">
         <v>10105</v>
       </c>
-      <c r="F10" s="10">
+      <c r="G10" s="10">
         <v>4</v>
       </c>
-      <c r="G10" s="10">
-        <v>0</v>
-      </c>
       <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
         <v>0.6</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="11">
         <v>775</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID10"/>
-    </row>
-    <row r="11" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M10" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE10"/>
+    </row>
+    <row r="11" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C11" s="8">
         <v>10105</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" s="8">
         <v>10106</v>
       </c>
-      <c r="F11" s="10">
+      <c r="G11" s="10">
         <v>5</v>
       </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
       <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
         <v>0.6</v>
       </c>
-      <c r="I11" s="11">
+      <c r="J11" s="11">
         <v>1020</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="10"/>
+      <c r="L11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="10">
+      <c r="M11" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C12" s="8">
         <v>10106</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="8">
         <v>10107</v>
       </c>
-      <c r="F12" s="10">
+      <c r="G12" s="10">
         <v>6</v>
       </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
       <c r="H12" s="10">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10">
         <v>0.6</v>
       </c>
-      <c r="I12" s="11">
+      <c r="J12" s="11">
         <v>1330</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="10"/>
+      <c r="L12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID12"/>
-    </row>
-    <row r="13" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M12" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE12"/>
+    </row>
+    <row r="13" spans="3:239" ht="19.5" customHeight="1">
       <c r="C13" s="8">
         <v>10107</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="8">
         <v>10108</v>
       </c>
-      <c r="F13" s="10">
+      <c r="G13" s="10">
         <v>7</v>
       </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
       <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
         <v>0.5</v>
       </c>
-      <c r="I13" s="11">
+      <c r="J13" s="11">
         <v>1680</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="10"/>
+      <c r="L13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID13"/>
-    </row>
-    <row r="14" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M13" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE13"/>
+    </row>
+    <row r="14" spans="3:239" ht="19.5" customHeight="1">
       <c r="C14" s="8">
         <v>10108</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" s="8">
         <v>10109</v>
       </c>
-      <c r="F14" s="10">
+      <c r="G14" s="10">
         <v>8</v>
       </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
       <c r="H14" s="10">
+        <v>0</v>
+      </c>
+      <c r="I14" s="10">
         <v>0.5</v>
       </c>
-      <c r="I14" s="11">
+      <c r="J14" s="11">
         <v>2070</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="10"/>
+      <c r="L14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID14"/>
-    </row>
-    <row r="15" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M14" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE14"/>
+    </row>
+    <row r="15" spans="3:239" ht="19.5" customHeight="1">
       <c r="C15" s="8">
         <v>10109</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="F15" s="8">
         <v>10110</v>
       </c>
-      <c r="F15" s="10">
+      <c r="G15" s="10">
         <v>9</v>
       </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
       <c r="H15" s="10">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10">
         <v>0.5</v>
       </c>
-      <c r="I15" s="11">
+      <c r="J15" s="11">
         <v>2500</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L15" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID15"/>
-    </row>
-    <row r="16" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M15" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE15"/>
+    </row>
+    <row r="16" spans="3:239" ht="19.5" customHeight="1">
       <c r="C16" s="8">
         <v>10110</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="F16" s="8">
         <v>10111</v>
       </c>
-      <c r="F16" s="10">
+      <c r="G16" s="10">
         <v>10</v>
       </c>
-      <c r="G16" s="10">
-        <v>0</v>
-      </c>
       <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
         <v>0.5</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="J16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="10"/>
+      <c r="L16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID16"/>
-    </row>
-    <row r="17" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M16" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE16"/>
+    </row>
+    <row r="17" spans="3:239" ht="19.5" customHeight="1">
       <c r="C17" s="8">
         <v>10111</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" s="8">
         <v>10112</v>
       </c>
-      <c r="F17" s="10">
+      <c r="G17" s="10">
         <v>11</v>
       </c>
-      <c r="G17" s="10">
-        <v>0</v>
-      </c>
       <c r="H17" s="10">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
         <v>0.5</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="J17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="10"/>
+      <c r="L17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="L17" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID17"/>
-    </row>
-    <row r="18" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M17" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE17"/>
+    </row>
+    <row r="18" spans="3:239" ht="19.5" customHeight="1">
       <c r="C18" s="8">
         <v>10112</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F18" s="8">
         <v>10113</v>
       </c>
-      <c r="F18" s="10">
+      <c r="G18" s="10">
         <v>12</v>
       </c>
-      <c r="G18" s="10">
-        <v>0</v>
-      </c>
       <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
         <v>0.5</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="J18" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="K18" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="L18" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID18"/>
-    </row>
-    <row r="19" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M18" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE18"/>
+    </row>
+    <row r="19" spans="3:239" ht="19.5" customHeight="1">
       <c r="C19" s="8">
         <v>10113</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="F19" s="8">
         <v>10114</v>
       </c>
-      <c r="F19" s="10">
+      <c r="G19" s="10">
         <v>13</v>
       </c>
-      <c r="G19" s="10">
-        <v>0</v>
-      </c>
       <c r="H19" s="10">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
         <v>0.5</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="J19" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="K19" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="L19" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="L19" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID19"/>
-    </row>
-    <row r="20" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M19" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE19"/>
+    </row>
+    <row r="20" spans="3:239" ht="19.5" customHeight="1">
       <c r="C20" s="8">
         <v>10114</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F20" s="8">
         <v>10115</v>
       </c>
-      <c r="F20" s="10">
+      <c r="G20" s="10">
         <v>14</v>
       </c>
-      <c r="G20" s="10">
-        <v>0</v>
-      </c>
       <c r="H20" s="10">
+        <v>0</v>
+      </c>
+      <c r="I20" s="10">
         <v>0.5</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="J20" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="K20" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="L20" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="L20" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID20"/>
-    </row>
-    <row r="21" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M20" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE20"/>
+    </row>
+    <row r="21" spans="3:239" ht="19.5" customHeight="1">
       <c r="C21" s="8">
         <v>10115</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="E21" s="8">
-        <v>0</v>
-      </c>
-      <c r="F21" s="10">
+      <c r="E21" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
         <v>15</v>
       </c>
-      <c r="G21" s="10">
-        <v>0</v>
-      </c>
       <c r="H21" s="10">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
         <v>0.5</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="J21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10" t="s">
+      <c r="K21" s="10"/>
+      <c r="L21" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="L21" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID21"/>
-    </row>
-    <row r="22" spans="3:238" ht="22.5" customHeight="1">
+      <c r="M21" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE21"/>
+    </row>
+    <row r="22" spans="3:239" ht="22.5" customHeight="1">
       <c r="C22" s="8">
         <v>10200</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="F22" s="8">
         <v>10201</v>
       </c>
-      <c r="F22" s="10">
-        <v>0</v>
-      </c>
       <c r="G22" s="10">
         <v>0</v>
       </c>
       <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
         <v>1</v>
       </c>
-      <c r="I22" s="11">
+      <c r="J22" s="11">
         <v>100</v>
       </c>
-      <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="10">
+      <c r="L22" s="10"/>
+      <c r="M22" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="23" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C23" s="8">
         <v>10201</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="F23" s="8">
         <v>10202</v>
       </c>
-      <c r="F23" s="10">
+      <c r="G23" s="10">
         <v>1</v>
       </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
       <c r="H23" s="10">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10">
         <v>0.8</v>
       </c>
-      <c r="I23" s="11">
+      <c r="J23" s="11">
         <v>220</v>
       </c>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10" t="s">
+      <c r="K23" s="10"/>
+      <c r="L23" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="L23" s="10">
+      <c r="M23" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C24" s="8">
         <v>10202</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F24" s="8">
         <v>10203</v>
       </c>
-      <c r="F24" s="10">
+      <c r="G24" s="10">
         <v>2</v>
       </c>
-      <c r="G24" s="10">
-        <v>0</v>
-      </c>
       <c r="H24" s="10">
+        <v>0</v>
+      </c>
+      <c r="I24" s="10">
         <v>0.7</v>
       </c>
-      <c r="I24" s="11">
+      <c r="J24" s="11">
         <v>375</v>
       </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="10"/>
+      <c r="L24" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="L24" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID24"/>
-    </row>
-    <row r="25" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M24" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE24"/>
+    </row>
+    <row r="25" spans="3:239" ht="19.5" customHeight="1">
       <c r="C25" s="8">
         <v>10203</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="8">
         <v>10204</v>
       </c>
-      <c r="F25" s="10">
+      <c r="G25" s="10">
         <v>3</v>
       </c>
-      <c r="G25" s="10">
-        <v>0</v>
-      </c>
       <c r="H25" s="10">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
         <v>0.6</v>
       </c>
-      <c r="I25" s="11">
+      <c r="J25" s="11">
         <v>560</v>
       </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="10"/>
+      <c r="L25" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L25" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID25"/>
-    </row>
-    <row r="26" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M25" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE25"/>
+    </row>
+    <row r="26" spans="3:239" ht="19.5" customHeight="1">
       <c r="C26" s="8">
         <v>10204</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26" s="8">
         <v>10205</v>
       </c>
-      <c r="F26" s="10">
+      <c r="G26" s="10">
         <v>4</v>
       </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
       <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
         <v>0.6</v>
       </c>
-      <c r="I26" s="11">
+      <c r="J26" s="11">
         <v>775</v>
       </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="10"/>
+      <c r="L26" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L26" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID26"/>
-    </row>
-    <row r="27" spans="3:238" ht="22.5" customHeight="1">
+      <c r="M26" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE26"/>
+    </row>
+    <row r="27" spans="3:239" ht="22.5" customHeight="1">
       <c r="C27" s="8">
         <v>10205</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="F27" s="8">
         <v>10206</v>
       </c>
-      <c r="F27" s="10">
+      <c r="G27" s="10">
         <v>5</v>
       </c>
-      <c r="G27" s="10">
-        <v>0</v>
-      </c>
       <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
         <v>1</v>
       </c>
-      <c r="I27" s="11">
+      <c r="J27" s="11">
         <v>1020</v>
       </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10" t="s">
+      <c r="K27" s="10"/>
+      <c r="L27" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="L27" s="10">
+      <c r="M27" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="28" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C28" s="8">
         <v>10206</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="F28" s="8">
         <v>10207</v>
       </c>
-      <c r="F28" s="10">
+      <c r="G28" s="10">
         <v>6</v>
       </c>
-      <c r="G28" s="10">
-        <v>0</v>
-      </c>
       <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
         <v>0.8</v>
       </c>
-      <c r="I28" s="11">
+      <c r="J28" s="11">
         <v>1330</v>
       </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="10"/>
+      <c r="L28" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="L28" s="10">
+      <c r="M28" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="29" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C29" s="8">
         <v>10207</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F29" s="8">
         <v>10208</v>
       </c>
-      <c r="F29" s="10">
+      <c r="G29" s="10">
         <v>7</v>
       </c>
-      <c r="G29" s="10">
-        <v>0</v>
-      </c>
       <c r="H29" s="10">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
         <v>0.7</v>
       </c>
-      <c r="I29" s="11">
+      <c r="J29" s="11">
         <v>1680</v>
       </c>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="10"/>
+      <c r="L29" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID29"/>
-    </row>
-    <row r="30" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M29" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE29"/>
+    </row>
+    <row r="30" spans="3:239" ht="19.5" customHeight="1">
       <c r="C30" s="8">
         <v>10208</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="F30" s="8">
         <v>10209</v>
       </c>
-      <c r="F30" s="10">
+      <c r="G30" s="10">
         <v>8</v>
       </c>
-      <c r="G30" s="10">
-        <v>0</v>
-      </c>
       <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
         <v>0.6</v>
       </c>
-      <c r="I30" s="11">
+      <c r="J30" s="11">
         <v>2070</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="10"/>
+      <c r="L30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L30" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID30"/>
-    </row>
-    <row r="31" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M30" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE30"/>
+    </row>
+    <row r="31" spans="3:239" ht="19.5" customHeight="1">
       <c r="C31" s="8">
         <v>10209</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F31" s="8">
         <v>10210</v>
       </c>
-      <c r="F31" s="10">
+      <c r="G31" s="10">
         <v>9</v>
       </c>
-      <c r="G31" s="10">
-        <v>0</v>
-      </c>
       <c r="H31" s="10">
+        <v>0</v>
+      </c>
+      <c r="I31" s="10">
         <v>0.6</v>
       </c>
-      <c r="I31" s="11">
+      <c r="J31" s="11">
         <v>2500</v>
       </c>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="10"/>
+      <c r="L31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L31" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID31"/>
-    </row>
-    <row r="32" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M31" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE31"/>
+    </row>
+    <row r="32" spans="3:239" ht="19.5" customHeight="1">
       <c r="C32" s="8">
         <v>10210</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F32" s="8">
         <v>10211</v>
       </c>
-      <c r="F32" s="10">
+      <c r="G32" s="10">
         <v>10</v>
       </c>
-      <c r="G32" s="10">
-        <v>0</v>
-      </c>
       <c r="H32" s="10">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
         <v>0.6</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="J32" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10" t="s">
+      <c r="K32" s="10"/>
+      <c r="L32" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="L32" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID32"/>
-    </row>
-    <row r="33" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M32" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE32"/>
+    </row>
+    <row r="33" spans="3:239" ht="19.5" customHeight="1">
       <c r="C33" s="8">
         <v>10211</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="F33" s="8">
         <v>10212</v>
       </c>
-      <c r="F33" s="10">
+      <c r="G33" s="10">
         <v>11</v>
       </c>
-      <c r="G33" s="10">
-        <v>0</v>
-      </c>
       <c r="H33" s="10">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10">
         <v>0.6</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="J33" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10" t="s">
+      <c r="K33" s="10"/>
+      <c r="L33" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L33" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="M33" s="2">
+      <c r="M33" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N33" s="2">
         <f>14400-12600</f>
         <v>1800</v>
       </c>
-      <c r="ID33"/>
-    </row>
-    <row r="34" spans="3:238" ht="19.5" customHeight="1">
+      <c r="IE33"/>
+    </row>
+    <row r="34" spans="3:239" ht="19.5" customHeight="1">
       <c r="C34" s="8">
         <v>10212</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" s="8">
         <v>10213</v>
       </c>
-      <c r="F34" s="10">
+      <c r="G34" s="10">
         <v>12</v>
       </c>
-      <c r="G34" s="10">
-        <v>0</v>
-      </c>
       <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
         <v>0.6</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="J34" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J34" s="10" t="s">
+      <c r="K34" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="L34" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="L34" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="M34" s="2">
+      <c r="M34" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N34" s="2">
         <v>14400</v>
       </c>
-      <c r="ID34"/>
-    </row>
-    <row r="35" spans="3:238" ht="19.5" customHeight="1">
+      <c r="IE34"/>
+    </row>
+    <row r="35" spans="3:239" ht="19.5" customHeight="1">
       <c r="C35" s="8">
         <v>10213</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F35" s="8">
         <v>10214</v>
       </c>
-      <c r="F35" s="10">
+      <c r="G35" s="10">
         <v>13</v>
       </c>
-      <c r="G35" s="10">
-        <v>0</v>
-      </c>
       <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
         <v>0.6</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="J35" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="K35" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="L35" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="L35" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="M35" s="2">
-        <f>M34+$M$33</f>
+      <c r="M35" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N35" s="2">
+        <f>N34+$N$33</f>
         <v>16200</v>
       </c>
-      <c r="ID35"/>
-    </row>
-    <row r="36" spans="3:238" ht="19.5" customHeight="1">
+      <c r="IE35"/>
+    </row>
+    <row r="36" spans="3:239" ht="19.5" customHeight="1">
       <c r="C36" s="8">
         <v>10214</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F36" s="8">
         <v>10215</v>
       </c>
-      <c r="F36" s="10">
+      <c r="G36" s="10">
         <v>14</v>
       </c>
-      <c r="G36" s="10">
-        <v>0</v>
-      </c>
       <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
         <v>0.6</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="J36" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="K36" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="L36" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="L36" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="M36" s="2">
-        <f t="shared" ref="M36:M37" si="0">M35+$M$33</f>
+      <c r="M36" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" ref="N36:N37" si="0">N35+$N$33</f>
         <v>18000</v>
       </c>
-      <c r="ID36"/>
-    </row>
-    <row r="37" spans="3:238" ht="19.5" customHeight="1">
+      <c r="IE36"/>
+    </row>
+    <row r="37" spans="3:239" ht="19.5" customHeight="1">
       <c r="C37" s="8">
         <v>10215</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E37" s="8">
-        <v>0</v>
-      </c>
-      <c r="F37" s="10">
+      <c r="E37" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="10">
         <v>15</v>
       </c>
-      <c r="G37" s="10">
-        <v>0</v>
-      </c>
       <c r="H37" s="10">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10">
         <v>0.6</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="J37" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="10"/>
+      <c r="L37" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="L37" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="M37" s="2">
+      <c r="M37" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N37" s="2">
         <f t="shared" si="0"/>
         <v>19800</v>
       </c>
-      <c r="ID37"/>
-    </row>
-    <row r="38" spans="3:238" ht="22.5" customHeight="1">
+      <c r="IE37"/>
+    </row>
+    <row r="38" spans="3:239" ht="22.5" customHeight="1">
       <c r="C38" s="8">
         <v>10300</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F38" s="8">
         <v>10301</v>
       </c>
-      <c r="F38" s="10">
-        <v>0</v>
-      </c>
       <c r="G38" s="10">
         <v>0</v>
       </c>
       <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
         <v>1</v>
       </c>
-      <c r="I38" s="11">
+      <c r="J38" s="11">
         <v>100</v>
       </c>
-      <c r="J38" s="10"/>
       <c r="K38" s="10"/>
-      <c r="L38" s="10">
+      <c r="L38" s="10"/>
+      <c r="M38" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="39" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C39" s="8">
         <v>10301</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F39" s="8">
         <v>10302</v>
       </c>
-      <c r="F39" s="10">
+      <c r="G39" s="10">
         <v>1</v>
       </c>
-      <c r="G39" s="10">
-        <v>0</v>
-      </c>
       <c r="H39" s="10">
+        <v>0</v>
+      </c>
+      <c r="I39" s="10">
         <v>0.8</v>
       </c>
-      <c r="I39" s="11">
+      <c r="J39" s="11">
         <v>220</v>
       </c>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10" t="s">
+      <c r="K39" s="10"/>
+      <c r="L39" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="L39" s="10">
+      <c r="M39" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="40" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C40" s="8">
         <v>10302</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F40" s="8">
         <v>10303</v>
       </c>
-      <c r="F40" s="10">
+      <c r="G40" s="10">
         <v>2</v>
       </c>
-      <c r="G40" s="10">
-        <v>0</v>
-      </c>
       <c r="H40" s="10">
+        <v>0</v>
+      </c>
+      <c r="I40" s="10">
         <v>0.7</v>
       </c>
-      <c r="I40" s="11">
+      <c r="J40" s="11">
         <v>375</v>
       </c>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10" t="s">
+      <c r="K40" s="10"/>
+      <c r="L40" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="L40" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID40"/>
-    </row>
-    <row r="41" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M40" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE40"/>
+    </row>
+    <row r="41" spans="3:239" ht="19.5" customHeight="1">
       <c r="C41" s="8">
         <v>10303</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="F41" s="8">
         <v>10304</v>
       </c>
-      <c r="F41" s="10">
+      <c r="G41" s="10">
         <v>3</v>
       </c>
-      <c r="G41" s="10">
-        <v>0</v>
-      </c>
       <c r="H41" s="10">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10">
         <v>0.6</v>
       </c>
-      <c r="I41" s="11">
+      <c r="J41" s="11">
         <v>560</v>
       </c>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10" t="s">
+      <c r="K41" s="10"/>
+      <c r="L41" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="L41" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID41"/>
-    </row>
-    <row r="42" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M41" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE41"/>
+    </row>
+    <row r="42" spans="3:239" ht="19.5" customHeight="1">
       <c r="C42" s="8">
         <v>10304</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="F42" s="8">
         <v>10305</v>
       </c>
-      <c r="F42" s="10">
+      <c r="G42" s="10">
         <v>4</v>
       </c>
-      <c r="G42" s="10">
-        <v>0</v>
-      </c>
       <c r="H42" s="10">
+        <v>0</v>
+      </c>
+      <c r="I42" s="10">
         <v>0.6</v>
       </c>
-      <c r="I42" s="11">
+      <c r="J42" s="11">
         <v>775</v>
       </c>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10" t="s">
+      <c r="K42" s="10"/>
+      <c r="L42" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="L42" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID42"/>
-    </row>
-    <row r="43" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M42" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE42"/>
+    </row>
+    <row r="43" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C43" s="8">
         <v>10305</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F43" s="8">
         <v>10306</v>
       </c>
-      <c r="F43" s="10">
+      <c r="G43" s="10">
         <v>5</v>
       </c>
-      <c r="G43" s="10">
-        <v>0</v>
-      </c>
       <c r="H43" s="10">
+        <v>0</v>
+      </c>
+      <c r="I43" s="10">
         <v>0.8</v>
       </c>
-      <c r="I43" s="11">
+      <c r="J43" s="11">
         <v>1020</v>
       </c>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10" t="s">
+      <c r="K43" s="10"/>
+      <c r="L43" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="L43" s="10">
+      <c r="M43" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="44" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="44" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C44" s="8">
         <v>10306</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="F44" s="8">
         <v>10307</v>
       </c>
-      <c r="F44" s="10">
+      <c r="G44" s="10">
         <v>6</v>
       </c>
-      <c r="G44" s="10">
-        <v>0</v>
-      </c>
       <c r="H44" s="10">
+        <v>0</v>
+      </c>
+      <c r="I44" s="10">
         <v>0.7</v>
       </c>
-      <c r="I44" s="11">
+      <c r="J44" s="11">
         <v>1330</v>
       </c>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10" t="s">
+      <c r="K44" s="10"/>
+      <c r="L44" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="L44" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID44"/>
-    </row>
-    <row r="45" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M44" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE44"/>
+    </row>
+    <row r="45" spans="3:239" ht="19.5" customHeight="1">
       <c r="C45" s="8">
         <v>10307</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="F45" s="8">
         <v>10308</v>
       </c>
-      <c r="F45" s="10">
+      <c r="G45" s="10">
         <v>7</v>
       </c>
-      <c r="G45" s="10">
-        <v>0</v>
-      </c>
       <c r="H45" s="10">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
         <v>0.6</v>
       </c>
-      <c r="I45" s="11">
+      <c r="J45" s="11">
         <v>1680</v>
       </c>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="10"/>
+      <c r="L45" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="L45" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID45"/>
-    </row>
-    <row r="46" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M45" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE45"/>
+    </row>
+    <row r="46" spans="3:239" ht="19.5" customHeight="1">
       <c r="C46" s="8">
         <v>10308</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F46" s="8">
         <v>10309</v>
       </c>
-      <c r="F46" s="10">
+      <c r="G46" s="10">
         <v>8</v>
       </c>
-      <c r="G46" s="10">
-        <v>0</v>
-      </c>
       <c r="H46" s="10">
+        <v>0</v>
+      </c>
+      <c r="I46" s="10">
         <v>0.6</v>
       </c>
-      <c r="I46" s="11">
+      <c r="J46" s="11">
         <v>2070</v>
       </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10" t="s">
+      <c r="K46" s="10"/>
+      <c r="L46" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L46" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID46"/>
-    </row>
-    <row r="47" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M46" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE46"/>
+    </row>
+    <row r="47" spans="3:239" ht="19.5" customHeight="1">
       <c r="C47" s="8">
         <v>10309</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="F47" s="8">
         <v>10310</v>
       </c>
-      <c r="F47" s="10">
+      <c r="G47" s="10">
         <v>9</v>
       </c>
-      <c r="G47" s="10">
-        <v>0</v>
-      </c>
       <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
         <v>0.6</v>
       </c>
-      <c r="I47" s="11">
+      <c r="J47" s="11">
         <v>2500</v>
       </c>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="10"/>
+      <c r="L47" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="L47" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID47"/>
-    </row>
-    <row r="48" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M47" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE47"/>
+    </row>
+    <row r="48" spans="3:239" ht="19.5" customHeight="1">
       <c r="C48" s="8">
         <v>10310</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="F48" s="8">
         <v>10311</v>
       </c>
-      <c r="F48" s="10">
+      <c r="G48" s="10">
         <v>10</v>
       </c>
-      <c r="G48" s="10">
-        <v>0</v>
-      </c>
       <c r="H48" s="10">
+        <v>0</v>
+      </c>
+      <c r="I48" s="10">
         <v>0.6</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="J48" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="10"/>
+      <c r="L48" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L48" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID48"/>
-    </row>
-    <row r="49" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M48" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE48"/>
+    </row>
+    <row r="49" spans="3:239" ht="19.5" customHeight="1">
       <c r="C49" s="8">
         <v>10311</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F49" s="8">
         <v>10312</v>
       </c>
-      <c r="F49" s="10">
+      <c r="G49" s="10">
         <v>11</v>
       </c>
-      <c r="G49" s="10">
-        <v>0</v>
-      </c>
       <c r="H49" s="10">
+        <v>0</v>
+      </c>
+      <c r="I49" s="10">
         <v>0.6</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="J49" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10" t="s">
+      <c r="K49" s="10"/>
+      <c r="L49" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="L49" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID49"/>
-    </row>
-    <row r="50" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M49" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE49"/>
+    </row>
+    <row r="50" spans="3:239" ht="19.5" customHeight="1">
       <c r="C50" s="8">
         <v>10312</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="F50" s="8">
         <v>10313</v>
       </c>
-      <c r="F50" s="10">
+      <c r="G50" s="10">
         <v>12</v>
       </c>
-      <c r="G50" s="10">
-        <v>0</v>
-      </c>
       <c r="H50" s="10">
+        <v>0</v>
+      </c>
+      <c r="I50" s="10">
         <v>0.6</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="J50" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="K50" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="L50" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="L50" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID50"/>
-    </row>
-    <row r="51" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M50" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE50"/>
+    </row>
+    <row r="51" spans="3:239" ht="19.5" customHeight="1">
       <c r="C51" s="8">
         <v>10313</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="F51" s="8">
         <v>10314</v>
       </c>
-      <c r="F51" s="10">
+      <c r="G51" s="10">
         <v>13</v>
       </c>
-      <c r="G51" s="10">
-        <v>0</v>
-      </c>
       <c r="H51" s="10">
+        <v>0</v>
+      </c>
+      <c r="I51" s="10">
         <v>0.6</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="J51" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="K51" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="L51" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="L51" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID51"/>
-    </row>
-    <row r="52" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M51" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE51"/>
+    </row>
+    <row r="52" spans="3:239" ht="19.5" customHeight="1">
       <c r="C52" s="8">
         <v>10314</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F52" s="8">
         <v>10315</v>
       </c>
-      <c r="F52" s="10">
+      <c r="G52" s="10">
         <v>14</v>
       </c>
-      <c r="G52" s="10">
-        <v>0</v>
-      </c>
       <c r="H52" s="10">
+        <v>0</v>
+      </c>
+      <c r="I52" s="10">
         <v>0.6</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="J52" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="K52" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="L52" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="L52" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID52"/>
-    </row>
-    <row r="53" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M52" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE52"/>
+    </row>
+    <row r="53" spans="3:239" ht="19.5" customHeight="1">
       <c r="C53" s="8">
         <v>10315</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="E53" s="8">
-        <v>0</v>
-      </c>
-      <c r="F53" s="10">
+      <c r="E53" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10">
         <v>15</v>
       </c>
-      <c r="G53" s="10">
-        <v>0</v>
-      </c>
       <c r="H53" s="10">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10">
         <v>0.6</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="J53" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="10"/>
+      <c r="L53" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="L53" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID53"/>
-    </row>
-    <row r="54" spans="3:238" ht="22.5" customHeight="1">
+      <c r="M53" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE53"/>
+    </row>
+    <row r="54" spans="3:239" ht="22.5" customHeight="1">
       <c r="C54" s="8">
         <v>10400</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F54" s="8">
         <v>10401</v>
       </c>
-      <c r="F54" s="10">
-        <v>0</v>
-      </c>
       <c r="G54" s="10">
         <v>0</v>
       </c>
       <c r="H54" s="10">
+        <v>0</v>
+      </c>
+      <c r="I54" s="10">
         <v>1</v>
       </c>
-      <c r="I54" s="11">
+      <c r="J54" s="11">
         <v>100</v>
       </c>
-      <c r="J54" s="10"/>
       <c r="K54" s="10"/>
-      <c r="L54" s="10">
+      <c r="L54" s="10"/>
+      <c r="M54" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="55" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="55" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C55" s="8">
         <v>10401</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F55" s="8">
         <v>10402</v>
       </c>
-      <c r="F55" s="10">
+      <c r="G55" s="10">
         <v>1</v>
       </c>
-      <c r="G55" s="10">
-        <v>0</v>
-      </c>
       <c r="H55" s="10">
+        <v>0</v>
+      </c>
+      <c r="I55" s="10">
         <v>0.8</v>
       </c>
-      <c r="I55" s="11">
+      <c r="J55" s="11">
         <v>220</v>
       </c>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="10"/>
+      <c r="L55" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="L55" s="10">
+      <c r="M55" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="56" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="56" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C56" s="8">
         <v>10402</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="F56" s="8">
         <v>10403</v>
       </c>
-      <c r="F56" s="10">
+      <c r="G56" s="10">
         <v>2</v>
       </c>
-      <c r="G56" s="10">
-        <v>0</v>
-      </c>
       <c r="H56" s="10">
+        <v>0</v>
+      </c>
+      <c r="I56" s="10">
         <v>0.7</v>
       </c>
-      <c r="I56" s="11">
+      <c r="J56" s="11">
         <v>375</v>
       </c>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="10"/>
+      <c r="L56" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="L56" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID56"/>
-    </row>
-    <row r="57" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M56" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE56"/>
+    </row>
+    <row r="57" spans="3:239" ht="19.5" customHeight="1">
       <c r="C57" s="8">
         <v>10403</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" s="8">
         <v>10404</v>
       </c>
-      <c r="F57" s="10">
+      <c r="G57" s="10">
         <v>3</v>
       </c>
-      <c r="G57" s="10">
-        <v>0</v>
-      </c>
       <c r="H57" s="10">
+        <v>0</v>
+      </c>
+      <c r="I57" s="10">
         <v>0.6</v>
       </c>
-      <c r="I57" s="11">
+      <c r="J57" s="11">
         <v>560</v>
       </c>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10" t="s">
+      <c r="K57" s="10"/>
+      <c r="L57" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="L57" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID57"/>
-    </row>
-    <row r="58" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M57" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE57"/>
+    </row>
+    <row r="58" spans="3:239" ht="19.5" customHeight="1">
       <c r="C58" s="8">
         <v>10404</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F58" s="8">
         <v>10405</v>
       </c>
-      <c r="F58" s="10">
+      <c r="G58" s="10">
         <v>4</v>
       </c>
-      <c r="G58" s="10">
-        <v>0</v>
-      </c>
       <c r="H58" s="10">
+        <v>0</v>
+      </c>
+      <c r="I58" s="10">
         <v>0.6</v>
       </c>
-      <c r="I58" s="11">
+      <c r="J58" s="11">
         <v>775</v>
       </c>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="10"/>
+      <c r="L58" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="L58" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID58"/>
-    </row>
-    <row r="59" spans="3:238" ht="22.5" customHeight="1">
+      <c r="M58" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE58"/>
+    </row>
+    <row r="59" spans="3:239" ht="22.5" customHeight="1">
       <c r="C59" s="8">
         <v>10405</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="F59" s="8">
         <v>10406</v>
       </c>
-      <c r="F59" s="10">
+      <c r="G59" s="10">
         <v>5</v>
       </c>
-      <c r="G59" s="10">
-        <v>0</v>
-      </c>
       <c r="H59" s="10">
+        <v>0</v>
+      </c>
+      <c r="I59" s="10">
         <v>1</v>
       </c>
-      <c r="I59" s="11">
+      <c r="J59" s="11">
         <v>1020</v>
       </c>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="10"/>
+      <c r="L59" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="L59" s="10">
+      <c r="M59" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="60" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C60" s="8">
         <v>10406</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="F60" s="8">
         <v>10407</v>
       </c>
-      <c r="F60" s="10">
+      <c r="G60" s="10">
         <v>6</v>
       </c>
-      <c r="G60" s="10">
-        <v>0</v>
-      </c>
       <c r="H60" s="10">
+        <v>0</v>
+      </c>
+      <c r="I60" s="10">
         <v>0.8</v>
       </c>
-      <c r="I60" s="11">
+      <c r="J60" s="11">
         <v>1330</v>
       </c>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="10"/>
+      <c r="L60" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="L60" s="10">
+      <c r="M60" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="61" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C61" s="8">
         <v>10407</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="F61" s="8">
         <v>10408</v>
       </c>
-      <c r="F61" s="10">
+      <c r="G61" s="10">
         <v>7</v>
       </c>
-      <c r="G61" s="10">
-        <v>0</v>
-      </c>
       <c r="H61" s="10">
+        <v>0</v>
+      </c>
+      <c r="I61" s="10">
         <v>0.7</v>
       </c>
-      <c r="I61" s="11">
+      <c r="J61" s="11">
         <v>1680</v>
       </c>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10" t="s">
+      <c r="K61" s="10"/>
+      <c r="L61" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="L61" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID61"/>
-    </row>
-    <row r="62" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M61" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE61"/>
+    </row>
+    <row r="62" spans="3:239" ht="19.5" customHeight="1">
       <c r="C62" s="8">
         <v>10408</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="F62" s="8">
         <v>10409</v>
       </c>
-      <c r="F62" s="10">
+      <c r="G62" s="10">
         <v>8</v>
       </c>
-      <c r="G62" s="10">
-        <v>0</v>
-      </c>
       <c r="H62" s="10">
+        <v>0</v>
+      </c>
+      <c r="I62" s="10">
         <v>0.6</v>
       </c>
-      <c r="I62" s="11">
+      <c r="J62" s="11">
         <v>2070</v>
       </c>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10" t="s">
+      <c r="K62" s="10"/>
+      <c r="L62" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="L62" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID62"/>
-    </row>
-    <row r="63" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M62" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE62"/>
+    </row>
+    <row r="63" spans="3:239" ht="19.5" customHeight="1">
       <c r="C63" s="8">
         <v>10409</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="F63" s="8">
         <v>10410</v>
       </c>
-      <c r="F63" s="10">
+      <c r="G63" s="10">
         <v>9</v>
       </c>
-      <c r="G63" s="10">
-        <v>0</v>
-      </c>
       <c r="H63" s="10">
+        <v>0</v>
+      </c>
+      <c r="I63" s="10">
         <v>0.6</v>
       </c>
-      <c r="I63" s="11">
+      <c r="J63" s="11">
         <v>2500</v>
       </c>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10" t="s">
+      <c r="K63" s="10"/>
+      <c r="L63" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="L63" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID63"/>
-    </row>
-    <row r="64" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M63" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE63"/>
+    </row>
+    <row r="64" spans="3:239" ht="19.5" customHeight="1">
       <c r="C64" s="8">
         <v>10410</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="F64" s="8">
         <v>10411</v>
       </c>
-      <c r="F64" s="10">
+      <c r="G64" s="10">
         <v>10</v>
       </c>
-      <c r="G64" s="10">
-        <v>0</v>
-      </c>
       <c r="H64" s="10">
+        <v>0</v>
+      </c>
+      <c r="I64" s="10">
         <v>0.6</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="J64" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10" t="s">
+      <c r="K64" s="10"/>
+      <c r="L64" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L64" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID64"/>
-    </row>
-    <row r="65" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M64" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE64"/>
+    </row>
+    <row r="65" spans="3:239" ht="19.5" customHeight="1">
       <c r="C65" s="8">
         <v>10411</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="F65" s="8">
         <v>10412</v>
       </c>
-      <c r="F65" s="10">
+      <c r="G65" s="10">
         <v>11</v>
       </c>
-      <c r="G65" s="10">
-        <v>0</v>
-      </c>
       <c r="H65" s="10">
+        <v>0</v>
+      </c>
+      <c r="I65" s="10">
         <v>0.6</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="J65" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10" t="s">
+      <c r="K65" s="10"/>
+      <c r="L65" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="L65" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID65"/>
-    </row>
-    <row r="66" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M65" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE65"/>
+    </row>
+    <row r="66" spans="3:239" ht="19.5" customHeight="1">
       <c r="C66" s="8">
         <v>10412</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F66" s="8">
         <v>10413</v>
       </c>
-      <c r="F66" s="10">
+      <c r="G66" s="10">
         <v>12</v>
       </c>
-      <c r="G66" s="10">
-        <v>0</v>
-      </c>
       <c r="H66" s="10">
+        <v>0</v>
+      </c>
+      <c r="I66" s="10">
         <v>0.6</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="J66" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J66" s="10" t="s">
+      <c r="K66" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K66" s="10" t="s">
+      <c r="L66" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="L66" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID66"/>
-    </row>
-    <row r="67" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M66" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE66"/>
+    </row>
+    <row r="67" spans="3:239" ht="19.5" customHeight="1">
       <c r="C67" s="8">
         <v>10413</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="F67" s="8">
         <v>10414</v>
       </c>
-      <c r="F67" s="10">
+      <c r="G67" s="10">
         <v>13</v>
       </c>
-      <c r="G67" s="10">
-        <v>0</v>
-      </c>
       <c r="H67" s="10">
+        <v>0</v>
+      </c>
+      <c r="I67" s="10">
         <v>0.6</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="J67" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J67" s="10" t="s">
+      <c r="K67" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K67" s="10" t="s">
+      <c r="L67" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="L67" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID67"/>
-    </row>
-    <row r="68" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M67" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE67"/>
+    </row>
+    <row r="68" spans="3:239" ht="19.5" customHeight="1">
       <c r="C68" s="8">
         <v>10414</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F68" s="8">
         <v>10415</v>
       </c>
-      <c r="F68" s="10">
+      <c r="G68" s="10">
         <v>14</v>
       </c>
-      <c r="G68" s="10">
-        <v>0</v>
-      </c>
       <c r="H68" s="10">
+        <v>0</v>
+      </c>
+      <c r="I68" s="10">
         <v>0.6</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="J68" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J68" s="10" t="s">
+      <c r="K68" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K68" s="10" t="s">
+      <c r="L68" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="L68" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID68"/>
-    </row>
-    <row r="69" spans="3:238" ht="19.5" customHeight="1">
+      <c r="M68" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE68"/>
+    </row>
+    <row r="69" spans="3:239" ht="19.5" customHeight="1">
       <c r="C69" s="8">
         <v>10415</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E69" s="8">
-        <v>0</v>
-      </c>
-      <c r="F69" s="10">
+      <c r="E69" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10">
         <v>15</v>
       </c>
-      <c r="G69" s="10">
-        <v>0</v>
-      </c>
       <c r="H69" s="10">
+        <v>0</v>
+      </c>
+      <c r="I69" s="10">
         <v>0.6</v>
       </c>
-      <c r="I69" s="11" t="s">
+      <c r="J69" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10" t="s">
+      <c r="K69" s="10"/>
+      <c r="L69" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="L69" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="ID69"/>
-    </row>
-    <row r="70" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M69" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE69"/>
+    </row>
+    <row r="70" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C70" s="8">
         <v>11100</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F70" s="8">
         <v>11101</v>
       </c>
-      <c r="F70" s="10">
-        <v>0</v>
-      </c>
       <c r="G70" s="10">
         <v>0</v>
       </c>
       <c r="H70" s="10">
+        <v>0</v>
+      </c>
+      <c r="I70" s="10">
         <v>1</v>
       </c>
-      <c r="I70" s="11">
+      <c r="J70" s="11">
         <v>100</v>
       </c>
-      <c r="J70" s="10" t="s">
+      <c r="K70" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10">
+      <c r="L70" s="10"/>
+      <c r="M70" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="71" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="71" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C71" s="8">
         <v>11101</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="F71" s="8">
         <v>11102</v>
       </c>
-      <c r="F71" s="10">
+      <c r="G71" s="10">
         <v>1</v>
       </c>
-      <c r="G71" s="10">
-        <v>0</v>
-      </c>
       <c r="H71" s="10">
+        <v>0</v>
+      </c>
+      <c r="I71" s="10">
         <v>0.8</v>
       </c>
-      <c r="I71" s="11">
+      <c r="J71" s="11">
         <v>220</v>
       </c>
-      <c r="J71" s="10" t="s">
+      <c r="K71" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="K71" s="10" t="s">
+      <c r="L71" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="L71" s="10">
+      <c r="M71" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="72" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="72" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C72" s="8">
         <v>11102</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="F72" s="8">
         <v>11103</v>
       </c>
-      <c r="F72" s="10">
+      <c r="G72" s="10">
         <v>2</v>
       </c>
-      <c r="G72" s="10">
-        <v>0</v>
-      </c>
       <c r="H72" s="10">
+        <v>0</v>
+      </c>
+      <c r="I72" s="10">
         <v>0.7</v>
       </c>
-      <c r="I72" s="11">
+      <c r="J72" s="11">
         <v>375</v>
       </c>
-      <c r="J72" s="10" t="s">
+      <c r="K72" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K72" s="10" t="s">
+      <c r="L72" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="L72" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="73" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M72" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="73" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C73" s="8">
         <v>11103</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="F73" s="8">
         <v>11104</v>
       </c>
-      <c r="F73" s="10">
+      <c r="G73" s="10">
         <v>3</v>
       </c>
-      <c r="G73" s="10">
-        <v>0</v>
-      </c>
       <c r="H73" s="10">
+        <v>0</v>
+      </c>
+      <c r="I73" s="10">
         <v>0.6</v>
       </c>
-      <c r="I73" s="11">
+      <c r="J73" s="11">
         <v>560</v>
       </c>
-      <c r="J73" s="10" t="s">
+      <c r="K73" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K73" s="10" t="s">
+      <c r="L73" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="L73" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="74" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M73" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="74" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C74" s="8">
         <v>11104</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="F74" s="8">
         <v>11105</v>
       </c>
-      <c r="F74" s="10">
+      <c r="G74" s="10">
         <v>4</v>
       </c>
-      <c r="G74" s="10">
-        <v>0</v>
-      </c>
       <c r="H74" s="10">
+        <v>0</v>
+      </c>
+      <c r="I74" s="10">
         <v>0.6</v>
       </c>
-      <c r="I74" s="11">
+      <c r="J74" s="11">
         <v>775</v>
       </c>
-      <c r="J74" s="10" t="s">
+      <c r="K74" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K74" s="10" t="s">
+      <c r="L74" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="L74" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="75" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M74" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="75" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C75" s="8">
         <v>11105</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="F75" s="8">
         <v>11106</v>
       </c>
-      <c r="F75" s="10">
+      <c r="G75" s="10">
         <v>5</v>
       </c>
-      <c r="G75" s="10">
-        <v>0</v>
-      </c>
       <c r="H75" s="10">
+        <v>0</v>
+      </c>
+      <c r="I75" s="10">
         <v>0.6</v>
       </c>
-      <c r="I75" s="11">
+      <c r="J75" s="11">
         <v>1020</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="K75" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K75" s="10" t="s">
+      <c r="L75" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="L75" s="10">
+      <c r="M75" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="76" spans="3:238" ht="20.100000000000001" customHeight="1">
+    <row r="76" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C76" s="8">
         <v>11106</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="F76" s="8">
         <v>11107</v>
       </c>
-      <c r="F76" s="10">
+      <c r="G76" s="10">
         <v>6</v>
       </c>
-      <c r="G76" s="10">
-        <v>0</v>
-      </c>
       <c r="H76" s="10">
+        <v>0</v>
+      </c>
+      <c r="I76" s="10">
         <v>0.6</v>
       </c>
-      <c r="I76" s="11">
+      <c r="J76" s="11">
         <v>1330</v>
       </c>
-      <c r="J76" s="10" t="s">
+      <c r="K76" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K76" s="10" t="s">
+      <c r="L76" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="L76" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="77" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M76" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="77" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C77" s="8">
         <v>11107</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="F77" s="8">
         <v>11108</v>
       </c>
-      <c r="F77" s="10">
+      <c r="G77" s="10">
         <v>7</v>
       </c>
-      <c r="G77" s="10">
-        <v>0</v>
-      </c>
       <c r="H77" s="10">
+        <v>0</v>
+      </c>
+      <c r="I77" s="10">
         <v>0.5</v>
       </c>
-      <c r="I77" s="11">
+      <c r="J77" s="11">
         <v>1680</v>
       </c>
-      <c r="J77" s="10" t="s">
+      <c r="K77" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="K77" s="10" t="s">
+      <c r="L77" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="L77" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="78" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M77" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="78" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C78" s="8">
         <v>11108</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F78" s="8">
         <v>11109</v>
       </c>
-      <c r="F78" s="10">
+      <c r="G78" s="10">
         <v>8</v>
       </c>
-      <c r="G78" s="10">
-        <v>0</v>
-      </c>
       <c r="H78" s="10">
+        <v>0</v>
+      </c>
+      <c r="I78" s="10">
         <v>0.5</v>
       </c>
-      <c r="I78" s="11">
+      <c r="J78" s="11">
         <v>2070</v>
       </c>
-      <c r="J78" s="10" t="s">
+      <c r="K78" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K78" s="10" t="s">
+      <c r="L78" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="L78" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="79" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M78" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="79" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C79" s="8">
         <v>11109</v>
       </c>
       <c r="D79" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="F79" s="8">
         <v>11110</v>
       </c>
-      <c r="F79" s="10">
+      <c r="G79" s="10">
         <v>9</v>
       </c>
-      <c r="G79" s="10">
-        <v>0</v>
-      </c>
       <c r="H79" s="10">
+        <v>0</v>
+      </c>
+      <c r="I79" s="10">
         <v>0.5</v>
       </c>
-      <c r="I79" s="11">
+      <c r="J79" s="11">
         <v>2500</v>
       </c>
-      <c r="J79" s="10" t="s">
+      <c r="K79" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K79" s="10" t="s">
+      <c r="L79" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="L79" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="80" spans="3:238" ht="20.100000000000001" customHeight="1">
+      <c r="M79" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="80" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C80" s="8">
         <v>11110</v>
       </c>
       <c r="D80" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="F80" s="8">
         <v>11111</v>
       </c>
-      <c r="F80" s="10">
+      <c r="G80" s="10">
         <v>10</v>
       </c>
-      <c r="G80" s="10">
-        <v>0</v>
-      </c>
       <c r="H80" s="10">
+        <v>0</v>
+      </c>
+      <c r="I80" s="10">
         <v>0.5</v>
       </c>
-      <c r="I80" s="11" t="s">
+      <c r="J80" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J80" s="10" t="s">
+      <c r="K80" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="K80" s="10" t="s">
+      <c r="L80" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="L80" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="81" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M80" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C81" s="8">
         <v>11111</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="F81" s="8">
         <v>11112</v>
       </c>
-      <c r="F81" s="10">
+      <c r="G81" s="10">
         <v>11</v>
       </c>
-      <c r="G81" s="10">
-        <v>0</v>
-      </c>
       <c r="H81" s="10">
+        <v>0</v>
+      </c>
+      <c r="I81" s="10">
         <v>0.5</v>
       </c>
-      <c r="I81" s="11" t="s">
+      <c r="J81" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J81" s="10" t="s">
+      <c r="K81" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K81" s="10" t="s">
+      <c r="L81" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="L81" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="82" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M81" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C82" s="8">
         <v>11112</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F82" s="8">
         <v>11113</v>
       </c>
-      <c r="F82" s="10">
+      <c r="G82" s="10">
         <v>12</v>
       </c>
-      <c r="G82" s="10">
-        <v>0</v>
-      </c>
       <c r="H82" s="10">
+        <v>0</v>
+      </c>
+      <c r="I82" s="10">
         <v>0.5</v>
       </c>
-      <c r="I82" s="11" t="s">
+      <c r="J82" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J82" s="10" t="s">
+      <c r="K82" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K82" s="10" t="s">
+      <c r="L82" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="L82" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="83" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M82" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="83" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C83" s="8">
         <v>11113</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="F83" s="8">
         <v>11114</v>
       </c>
-      <c r="F83" s="10">
+      <c r="G83" s="10">
         <v>13</v>
       </c>
-      <c r="G83" s="10">
-        <v>0</v>
-      </c>
       <c r="H83" s="10">
+        <v>0</v>
+      </c>
+      <c r="I83" s="10">
         <v>0.5</v>
       </c>
-      <c r="I83" s="11" t="s">
+      <c r="J83" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J83" s="10" t="s">
+      <c r="K83" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K83" s="10" t="s">
+      <c r="L83" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="L83" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="84" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M83" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C84" s="8">
         <v>11114</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="F84" s="8">
         <v>11115</v>
       </c>
-      <c r="F84" s="10">
+      <c r="G84" s="10">
         <v>14</v>
       </c>
-      <c r="G84" s="10">
-        <v>0</v>
-      </c>
       <c r="H84" s="10">
+        <v>0</v>
+      </c>
+      <c r="I84" s="10">
         <v>0.5</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="J84" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J84" s="10" t="s">
+      <c r="K84" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K84" s="10" t="s">
+      <c r="L84" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="L84" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="85" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M84" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C85" s="8">
         <v>11115</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="E85" s="8">
-        <v>0</v>
-      </c>
-      <c r="F85" s="10">
+      <c r="E85" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="F85" s="8">
+        <v>0</v>
+      </c>
+      <c r="G85" s="10">
         <v>15</v>
       </c>
-      <c r="G85" s="10">
-        <v>0</v>
-      </c>
       <c r="H85" s="10">
+        <v>0</v>
+      </c>
+      <c r="I85" s="10">
         <v>0.5</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="J85" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J85" s="10">
-        <v>0</v>
-      </c>
-      <c r="K85" s="10" t="s">
+      <c r="K85" s="10">
+        <v>0</v>
+      </c>
+      <c r="L85" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="L85" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="86" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M85" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C86" s="8">
         <v>11200</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="F86" s="8">
         <v>11201</v>
       </c>
-      <c r="F86" s="10">
-        <v>0</v>
-      </c>
       <c r="G86" s="10">
         <v>0</v>
       </c>
       <c r="H86" s="10">
+        <v>0</v>
+      </c>
+      <c r="I86" s="10">
         <v>1</v>
       </c>
-      <c r="I86" s="11">
+      <c r="J86" s="11">
         <v>100</v>
       </c>
-      <c r="J86" s="10" t="s">
+      <c r="K86" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K86" s="10"/>
-      <c r="L86" s="10">
+      <c r="L86" s="10"/>
+      <c r="M86" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="87" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C87" s="8">
         <v>11201</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="F87" s="8">
         <v>11202</v>
       </c>
-      <c r="F87" s="10">
+      <c r="G87" s="10">
         <v>1</v>
       </c>
-      <c r="G87" s="10">
-        <v>0</v>
-      </c>
       <c r="H87" s="10">
+        <v>0</v>
+      </c>
+      <c r="I87" s="10">
         <v>0.8</v>
       </c>
-      <c r="I87" s="11">
+      <c r="J87" s="11">
         <v>220</v>
       </c>
-      <c r="J87" s="10" t="s">
+      <c r="K87" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="L87" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="L87" s="10">
+      <c r="M87" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="88" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="88" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C88" s="8">
         <v>11202</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="F88" s="8">
         <v>11203</v>
       </c>
-      <c r="F88" s="10">
+      <c r="G88" s="10">
         <v>2</v>
       </c>
-      <c r="G88" s="10">
-        <v>0</v>
-      </c>
       <c r="H88" s="10">
+        <v>0</v>
+      </c>
+      <c r="I88" s="10">
         <v>0.7</v>
       </c>
-      <c r="I88" s="11">
+      <c r="J88" s="11">
         <v>375</v>
       </c>
-      <c r="J88" s="10" t="s">
+      <c r="K88" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K88" s="10" t="s">
+      <c r="L88" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="L88" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="89" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M88" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C89" s="8">
         <v>11203</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="F89" s="8">
         <v>11204</v>
       </c>
-      <c r="F89" s="10">
+      <c r="G89" s="10">
         <v>3</v>
       </c>
-      <c r="G89" s="10">
-        <v>0</v>
-      </c>
       <c r="H89" s="10">
+        <v>0</v>
+      </c>
+      <c r="I89" s="10">
         <v>0.6</v>
       </c>
-      <c r="I89" s="11">
+      <c r="J89" s="11">
         <v>560</v>
       </c>
-      <c r="J89" s="10" t="s">
+      <c r="K89" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K89" s="10" t="s">
+      <c r="L89" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="L89" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="90" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M89" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C90" s="8">
         <v>11204</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="F90" s="8">
         <v>11205</v>
       </c>
-      <c r="F90" s="10">
+      <c r="G90" s="10">
         <v>4</v>
       </c>
-      <c r="G90" s="10">
-        <v>0</v>
-      </c>
       <c r="H90" s="10">
+        <v>0</v>
+      </c>
+      <c r="I90" s="10">
         <v>0.6</v>
       </c>
-      <c r="I90" s="11">
+      <c r="J90" s="11">
         <v>775</v>
       </c>
-      <c r="J90" s="10" t="s">
+      <c r="K90" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K90" s="10" t="s">
+      <c r="L90" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="L90" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="91" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M90" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="91" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C91" s="8">
         <v>11205</v>
       </c>
       <c r="D91" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="F91" s="8">
         <v>11206</v>
       </c>
-      <c r="F91" s="10">
+      <c r="G91" s="10">
         <v>5</v>
       </c>
-      <c r="G91" s="10">
-        <v>0</v>
-      </c>
       <c r="H91" s="10">
+        <v>0</v>
+      </c>
+      <c r="I91" s="10">
         <v>1</v>
       </c>
-      <c r="I91" s="11">
+      <c r="J91" s="11">
         <v>1020</v>
       </c>
-      <c r="J91" s="10" t="s">
+      <c r="K91" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K91" s="10" t="s">
+      <c r="L91" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="L91" s="10">
+      <c r="M91" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="92" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C92" s="8">
         <v>11206</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="F92" s="8">
         <v>11207</v>
       </c>
-      <c r="F92" s="10">
+      <c r="G92" s="10">
         <v>6</v>
       </c>
-      <c r="G92" s="10">
-        <v>0</v>
-      </c>
       <c r="H92" s="10">
+        <v>0</v>
+      </c>
+      <c r="I92" s="10">
         <v>0.8</v>
       </c>
-      <c r="I92" s="11">
+      <c r="J92" s="11">
         <v>1330</v>
       </c>
-      <c r="J92" s="10" t="s">
+      <c r="K92" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K92" s="10" t="s">
+      <c r="L92" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="L92" s="10">
+      <c r="M92" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="93" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C93" s="8">
         <v>11207</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="F93" s="8">
         <v>11208</v>
       </c>
-      <c r="F93" s="10">
+      <c r="G93" s="10">
         <v>7</v>
       </c>
-      <c r="G93" s="10">
-        <v>0</v>
-      </c>
       <c r="H93" s="10">
+        <v>0</v>
+      </c>
+      <c r="I93" s="10">
         <v>0.7</v>
       </c>
-      <c r="I93" s="11">
+      <c r="J93" s="11">
         <v>1680</v>
       </c>
-      <c r="J93" s="10" t="s">
+      <c r="K93" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="K93" s="10" t="s">
+      <c r="L93" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="L93" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="94" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M93" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C94" s="8">
         <v>11208</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="F94" s="8">
         <v>11209</v>
       </c>
-      <c r="F94" s="10">
+      <c r="G94" s="10">
         <v>8</v>
       </c>
-      <c r="G94" s="10">
-        <v>0</v>
-      </c>
       <c r="H94" s="10">
+        <v>0</v>
+      </c>
+      <c r="I94" s="10">
         <v>0.6</v>
       </c>
-      <c r="I94" s="11">
+      <c r="J94" s="11">
         <v>2070</v>
       </c>
-      <c r="J94" s="10" t="s">
+      <c r="K94" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K94" s="10" t="s">
+      <c r="L94" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="L94" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="95" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M94" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C95" s="8">
         <v>11209</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="F95" s="8">
         <v>11210</v>
       </c>
-      <c r="F95" s="10">
+      <c r="G95" s="10">
         <v>9</v>
       </c>
-      <c r="G95" s="10">
-        <v>0</v>
-      </c>
       <c r="H95" s="10">
+        <v>0</v>
+      </c>
+      <c r="I95" s="10">
         <v>0.6</v>
       </c>
-      <c r="I95" s="11">
+      <c r="J95" s="11">
         <v>2500</v>
       </c>
-      <c r="J95" s="10" t="s">
+      <c r="K95" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K95" s="10" t="s">
+      <c r="L95" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="L95" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="96" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M95" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="96" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C96" s="8">
         <v>11210</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F96" s="8">
         <v>11211</v>
       </c>
-      <c r="F96" s="10">
+      <c r="G96" s="10">
         <v>10</v>
       </c>
-      <c r="G96" s="10">
-        <v>0</v>
-      </c>
       <c r="H96" s="10">
+        <v>0</v>
+      </c>
+      <c r="I96" s="10">
         <v>0.6</v>
       </c>
-      <c r="I96" s="11" t="s">
+      <c r="J96" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J96" s="10" t="s">
+      <c r="K96" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="K96" s="10" t="s">
+      <c r="L96" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="L96" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="97" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M96" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C97" s="8">
         <v>11211</v>
       </c>
       <c r="D97" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="F97" s="8">
         <v>11212</v>
       </c>
-      <c r="F97" s="10">
+      <c r="G97" s="10">
         <v>11</v>
       </c>
-      <c r="G97" s="10">
-        <v>0</v>
-      </c>
       <c r="H97" s="10">
+        <v>0</v>
+      </c>
+      <c r="I97" s="10">
         <v>0.6</v>
       </c>
-      <c r="I97" s="11" t="s">
+      <c r="J97" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J97" s="10" t="s">
+      <c r="K97" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K97" s="10" t="s">
+      <c r="L97" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="L97" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="98" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M97" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C98" s="8">
         <v>11212</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="F98" s="8">
         <v>11213</v>
       </c>
-      <c r="F98" s="10">
+      <c r="G98" s="10">
         <v>12</v>
       </c>
-      <c r="G98" s="10">
-        <v>0</v>
-      </c>
       <c r="H98" s="10">
+        <v>0</v>
+      </c>
+      <c r="I98" s="10">
         <v>0.6</v>
       </c>
-      <c r="I98" s="11" t="s">
+      <c r="J98" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J98" s="10" t="s">
+      <c r="K98" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K98" s="10" t="s">
+      <c r="L98" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="L98" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="99" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M98" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C99" s="8">
         <v>11213</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="F99" s="8">
         <v>11214</v>
       </c>
-      <c r="F99" s="10">
+      <c r="G99" s="10">
         <v>13</v>
       </c>
-      <c r="G99" s="10">
-        <v>0</v>
-      </c>
       <c r="H99" s="10">
+        <v>0</v>
+      </c>
+      <c r="I99" s="10">
         <v>0.6</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="J99" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J99" s="10" t="s">
+      <c r="K99" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K99" s="10" t="s">
+      <c r="L99" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="L99" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="100" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M99" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C100" s="8">
         <v>11214</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E100" s="8">
+      <c r="E100" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="F100" s="8">
         <v>11215</v>
       </c>
-      <c r="F100" s="10">
+      <c r="G100" s="10">
         <v>14</v>
       </c>
-      <c r="G100" s="10">
-        <v>0</v>
-      </c>
       <c r="H100" s="10">
+        <v>0</v>
+      </c>
+      <c r="I100" s="10">
         <v>0.6</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="J100" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J100" s="10" t="s">
+      <c r="K100" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K100" s="10" t="s">
+      <c r="L100" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="L100" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M100" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C101" s="8">
         <v>11215</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="E101" s="8">
-        <v>0</v>
-      </c>
-      <c r="F101" s="10">
+      <c r="E101" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="F101" s="8">
+        <v>0</v>
+      </c>
+      <c r="G101" s="10">
         <v>15</v>
       </c>
-      <c r="G101" s="10">
-        <v>0</v>
-      </c>
       <c r="H101" s="10">
+        <v>0</v>
+      </c>
+      <c r="I101" s="10">
         <v>0.6</v>
       </c>
-      <c r="I101" s="11" t="s">
+      <c r="J101" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J101" s="10">
-        <v>0</v>
-      </c>
-      <c r="K101" s="10" t="s">
+      <c r="K101" s="10">
+        <v>0</v>
+      </c>
+      <c r="L101" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="L101" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M101" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C102" s="8">
         <v>11300</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E102" s="8">
+      <c r="E102" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="F102" s="8">
         <v>11301</v>
       </c>
-      <c r="F102" s="10">
-        <v>0</v>
-      </c>
       <c r="G102" s="10">
         <v>0</v>
       </c>
       <c r="H102" s="10">
+        <v>0</v>
+      </c>
+      <c r="I102" s="10">
         <v>1</v>
       </c>
-      <c r="I102" s="11">
+      <c r="J102" s="11">
         <v>100</v>
       </c>
-      <c r="J102" s="10" t="s">
+      <c r="K102" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K102" s="10"/>
-      <c r="L102" s="10">
+      <c r="L102" s="10"/>
+      <c r="M102" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="103" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="103" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C103" s="8">
         <v>11301</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="F103" s="8">
         <v>11302</v>
       </c>
-      <c r="F103" s="10">
+      <c r="G103" s="10">
         <v>1</v>
       </c>
-      <c r="G103" s="10">
-        <v>0</v>
-      </c>
       <c r="H103" s="10">
+        <v>0</v>
+      </c>
+      <c r="I103" s="10">
         <v>0.8</v>
       </c>
-      <c r="I103" s="11">
+      <c r="J103" s="11">
         <v>220</v>
       </c>
-      <c r="J103" s="10" t="s">
+      <c r="K103" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="K103" s="10" t="s">
+      <c r="L103" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="L103" s="10">
+      <c r="M103" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="104" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="104" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C104" s="8">
         <v>11302</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F104" s="8">
         <v>11303</v>
       </c>
-      <c r="F104" s="10">
+      <c r="G104" s="10">
         <v>2</v>
       </c>
-      <c r="G104" s="10">
-        <v>0</v>
-      </c>
       <c r="H104" s="10">
+        <v>0</v>
+      </c>
+      <c r="I104" s="10">
         <v>0.7</v>
       </c>
-      <c r="I104" s="11">
+      <c r="J104" s="11">
         <v>375</v>
       </c>
-      <c r="J104" s="10" t="s">
+      <c r="K104" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K104" s="10" t="s">
+      <c r="L104" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="L104" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="105" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M104" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="105" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C105" s="8">
         <v>11303</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="F105" s="8">
         <v>11304</v>
       </c>
-      <c r="F105" s="10">
+      <c r="G105" s="10">
         <v>3</v>
       </c>
-      <c r="G105" s="10">
-        <v>0</v>
-      </c>
       <c r="H105" s="10">
+        <v>0</v>
+      </c>
+      <c r="I105" s="10">
         <v>0.6</v>
       </c>
-      <c r="I105" s="11">
+      <c r="J105" s="11">
         <v>560</v>
       </c>
-      <c r="J105" s="10" t="s">
+      <c r="K105" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K105" s="10" t="s">
+      <c r="L105" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="L105" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="106" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M105" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="106" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C106" s="8">
         <v>11304</v>
       </c>
       <c r="D106" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="F106" s="8">
         <v>11305</v>
       </c>
-      <c r="F106" s="10">
+      <c r="G106" s="10">
         <v>4</v>
       </c>
-      <c r="G106" s="10">
-        <v>0</v>
-      </c>
       <c r="H106" s="10">
+        <v>0</v>
+      </c>
+      <c r="I106" s="10">
         <v>0.6</v>
       </c>
-      <c r="I106" s="11">
+      <c r="J106" s="11">
         <v>775</v>
       </c>
-      <c r="J106" s="10" t="s">
+      <c r="K106" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K106" s="10" t="s">
+      <c r="L106" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="L106" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="107" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M106" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="107" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C107" s="8">
         <v>11305</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E107" s="8">
+      <c r="E107" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="F107" s="8">
         <v>11306</v>
       </c>
-      <c r="F107" s="10">
+      <c r="G107" s="10">
         <v>5</v>
       </c>
-      <c r="G107" s="10">
-        <v>0</v>
-      </c>
       <c r="H107" s="10">
+        <v>0</v>
+      </c>
+      <c r="I107" s="10">
         <v>0.8</v>
       </c>
-      <c r="I107" s="11">
+      <c r="J107" s="11">
         <v>1020</v>
       </c>
-      <c r="J107" s="10" t="s">
+      <c r="K107" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K107" s="10" t="s">
+      <c r="L107" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L107" s="10">
+      <c r="M107" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="108" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C108" s="8">
         <v>11306</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E108" s="8">
+      <c r="E108" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="F108" s="8">
         <v>11307</v>
       </c>
-      <c r="F108" s="10">
+      <c r="G108" s="10">
         <v>6</v>
       </c>
-      <c r="G108" s="10">
-        <v>0</v>
-      </c>
       <c r="H108" s="10">
+        <v>0</v>
+      </c>
+      <c r="I108" s="10">
         <v>0.7</v>
       </c>
-      <c r="I108" s="11">
+      <c r="J108" s="11">
         <v>1330</v>
       </c>
-      <c r="J108" s="10" t="s">
+      <c r="K108" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K108" s="10" t="s">
+      <c r="L108" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="L108" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="109" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M108" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="109" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C109" s="8">
         <v>11307</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="F109" s="8">
         <v>11308</v>
       </c>
-      <c r="F109" s="10">
+      <c r="G109" s="10">
         <v>7</v>
       </c>
-      <c r="G109" s="10">
-        <v>0</v>
-      </c>
       <c r="H109" s="10">
+        <v>0</v>
+      </c>
+      <c r="I109" s="10">
         <v>0.6</v>
       </c>
-      <c r="I109" s="11">
+      <c r="J109" s="11">
         <v>1680</v>
       </c>
-      <c r="J109" s="10" t="s">
+      <c r="K109" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="K109" s="10" t="s">
+      <c r="L109" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="L109" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="110" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M109" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="110" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C110" s="8">
         <v>11308</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="F110" s="8">
         <v>11309</v>
       </c>
-      <c r="F110" s="10">
+      <c r="G110" s="10">
         <v>8</v>
       </c>
-      <c r="G110" s="10">
-        <v>0</v>
-      </c>
       <c r="H110" s="10">
+        <v>0</v>
+      </c>
+      <c r="I110" s="10">
         <v>0.6</v>
       </c>
-      <c r="I110" s="11">
+      <c r="J110" s="11">
         <v>2070</v>
       </c>
-      <c r="J110" s="10" t="s">
+      <c r="K110" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K110" s="10" t="s">
+      <c r="L110" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="L110" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="111" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M110" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="111" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C111" s="8">
         <v>11309</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="F111" s="8">
         <v>11310</v>
       </c>
-      <c r="F111" s="10">
+      <c r="G111" s="10">
         <v>9</v>
       </c>
-      <c r="G111" s="10">
-        <v>0</v>
-      </c>
       <c r="H111" s="10">
+        <v>0</v>
+      </c>
+      <c r="I111" s="10">
         <v>0.6</v>
       </c>
-      <c r="I111" s="11">
+      <c r="J111" s="11">
         <v>2500</v>
       </c>
-      <c r="J111" s="10" t="s">
+      <c r="K111" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K111" s="10" t="s">
+      <c r="L111" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="L111" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="112" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M111" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="112" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C112" s="8">
         <v>11310</v>
       </c>
       <c r="D112" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E112" s="8">
+      <c r="E112" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="F112" s="8">
         <v>11311</v>
       </c>
-      <c r="F112" s="10">
+      <c r="G112" s="10">
         <v>10</v>
       </c>
-      <c r="G112" s="10">
-        <v>0</v>
-      </c>
       <c r="H112" s="10">
+        <v>0</v>
+      </c>
+      <c r="I112" s="10">
         <v>0.6</v>
       </c>
-      <c r="I112" s="11" t="s">
+      <c r="J112" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J112" s="10" t="s">
+      <c r="K112" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="K112" s="10" t="s">
+      <c r="L112" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="L112" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="113" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M112" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="113" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C113" s="8">
         <v>11311</v>
       </c>
       <c r="D113" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E113" s="8">
+      <c r="E113" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="F113" s="8">
         <v>11312</v>
       </c>
-      <c r="F113" s="10">
+      <c r="G113" s="10">
         <v>11</v>
       </c>
-      <c r="G113" s="10">
-        <v>0</v>
-      </c>
       <c r="H113" s="10">
+        <v>0</v>
+      </c>
+      <c r="I113" s="10">
         <v>0.6</v>
       </c>
-      <c r="I113" s="11" t="s">
+      <c r="J113" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J113" s="10" t="s">
+      <c r="K113" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K113" s="10" t="s">
+      <c r="L113" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="L113" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="114" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M113" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="114" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C114" s="8">
         <v>11312</v>
       </c>
       <c r="D114" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E114" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="F114" s="8">
         <v>11313</v>
       </c>
-      <c r="F114" s="10">
+      <c r="G114" s="10">
         <v>12</v>
       </c>
-      <c r="G114" s="10">
-        <v>0</v>
-      </c>
       <c r="H114" s="10">
+        <v>0</v>
+      </c>
+      <c r="I114" s="10">
         <v>0.6</v>
       </c>
-      <c r="I114" s="11" t="s">
+      <c r="J114" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J114" s="10" t="s">
+      <c r="K114" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K114" s="10" t="s">
+      <c r="L114" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="L114" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="115" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M114" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="115" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C115" s="8">
         <v>11313</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="F115" s="8">
         <v>11314</v>
       </c>
-      <c r="F115" s="10">
+      <c r="G115" s="10">
         <v>13</v>
       </c>
-      <c r="G115" s="10">
-        <v>0</v>
-      </c>
       <c r="H115" s="10">
+        <v>0</v>
+      </c>
+      <c r="I115" s="10">
         <v>0.6</v>
       </c>
-      <c r="I115" s="11" t="s">
+      <c r="J115" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J115" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K115" s="10" t="s">
+      <c r="L115" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="L115" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="116" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M115" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="116" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C116" s="8">
         <v>11314</v>
       </c>
       <c r="D116" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="F116" s="8">
         <v>11315</v>
       </c>
-      <c r="F116" s="10">
+      <c r="G116" s="10">
         <v>14</v>
       </c>
-      <c r="G116" s="10">
-        <v>0</v>
-      </c>
       <c r="H116" s="10">
+        <v>0</v>
+      </c>
+      <c r="I116" s="10">
         <v>0.6</v>
       </c>
-      <c r="I116" s="11" t="s">
+      <c r="J116" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J116" s="10" t="s">
+      <c r="K116" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K116" s="10" t="s">
+      <c r="L116" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="L116" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="117" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M116" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="117" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C117" s="8">
         <v>11315</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E117" s="8">
-        <v>0</v>
-      </c>
-      <c r="F117" s="10">
+      <c r="E117" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="F117" s="8">
+        <v>0</v>
+      </c>
+      <c r="G117" s="10">
         <v>15</v>
       </c>
-      <c r="G117" s="10">
-        <v>0</v>
-      </c>
       <c r="H117" s="10">
+        <v>0</v>
+      </c>
+      <c r="I117" s="10">
         <v>0.6</v>
       </c>
-      <c r="I117" s="11" t="s">
+      <c r="J117" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J117" s="10">
-        <v>0</v>
-      </c>
-      <c r="K117" s="10" t="s">
+      <c r="K117" s="10">
+        <v>0</v>
+      </c>
+      <c r="L117" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="L117" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="118" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M117" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="118" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C118" s="8">
         <v>11400</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E118" s="8">
+      <c r="E118" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F118" s="8">
         <v>11401</v>
       </c>
-      <c r="F118" s="10">
-        <v>0</v>
-      </c>
       <c r="G118" s="10">
         <v>0</v>
       </c>
       <c r="H118" s="10">
+        <v>0</v>
+      </c>
+      <c r="I118" s="10">
         <v>1</v>
       </c>
-      <c r="I118" s="11">
+      <c r="J118" s="11">
         <v>100</v>
       </c>
-      <c r="J118" s="10" t="s">
+      <c r="K118" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K118" s="10"/>
-      <c r="L118" s="10">
+      <c r="L118" s="10"/>
+      <c r="M118" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="119" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="119" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C119" s="8">
         <v>11401</v>
       </c>
       <c r="D119" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E119" s="8">
+      <c r="E119" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="F119" s="8">
         <v>11402</v>
       </c>
-      <c r="F119" s="10">
+      <c r="G119" s="10">
         <v>1</v>
       </c>
-      <c r="G119" s="10">
-        <v>0</v>
-      </c>
       <c r="H119" s="10">
+        <v>0</v>
+      </c>
+      <c r="I119" s="10">
         <v>0.8</v>
       </c>
-      <c r="I119" s="11">
+      <c r="J119" s="11">
         <v>220</v>
       </c>
-      <c r="J119" s="10" t="s">
+      <c r="K119" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="K119" s="10" t="s">
+      <c r="L119" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="L119" s="10">
+      <c r="M119" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="120" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C120" s="8">
         <v>11402</v>
       </c>
       <c r="D120" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E120" s="8">
+      <c r="E120" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="F120" s="8">
         <v>11403</v>
       </c>
-      <c r="F120" s="10">
+      <c r="G120" s="10">
         <v>2</v>
       </c>
-      <c r="G120" s="10">
-        <v>0</v>
-      </c>
       <c r="H120" s="10">
+        <v>0</v>
+      </c>
+      <c r="I120" s="10">
         <v>0.7</v>
       </c>
-      <c r="I120" s="11">
+      <c r="J120" s="11">
         <v>375</v>
       </c>
-      <c r="J120" s="10" t="s">
+      <c r="K120" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K120" s="10" t="s">
+      <c r="L120" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L120" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="121" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M120" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="121" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C121" s="8">
         <v>11403</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E121" s="8">
+      <c r="E121" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F121" s="8">
         <v>11404</v>
       </c>
-      <c r="F121" s="10">
+      <c r="G121" s="10">
         <v>3</v>
       </c>
-      <c r="G121" s="10">
-        <v>0</v>
-      </c>
       <c r="H121" s="10">
+        <v>0</v>
+      </c>
+      <c r="I121" s="10">
         <v>0.6</v>
       </c>
-      <c r="I121" s="11">
+      <c r="J121" s="11">
         <v>560</v>
       </c>
-      <c r="J121" s="10" t="s">
+      <c r="K121" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="K121" s="10" t="s">
+      <c r="L121" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="L121" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="122" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M121" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="122" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C122" s="8">
         <v>11404</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E122" s="8">
+      <c r="E122" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="F122" s="8">
         <v>11405</v>
       </c>
-      <c r="F122" s="10">
+      <c r="G122" s="10">
         <v>4</v>
       </c>
-      <c r="G122" s="10">
-        <v>0</v>
-      </c>
       <c r="H122" s="10">
+        <v>0</v>
+      </c>
+      <c r="I122" s="10">
         <v>0.6</v>
       </c>
-      <c r="I122" s="11">
+      <c r="J122" s="11">
         <v>775</v>
       </c>
-      <c r="J122" s="10" t="s">
+      <c r="K122" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="K122" s="10" t="s">
+      <c r="L122" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="L122" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="123" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M122" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="123" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C123" s="8">
         <v>11405</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E123" s="8">
+      <c r="E123" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="F123" s="8">
         <v>11406</v>
       </c>
-      <c r="F123" s="10">
+      <c r="G123" s="10">
         <v>5</v>
       </c>
-      <c r="G123" s="10">
-        <v>0</v>
-      </c>
       <c r="H123" s="10">
+        <v>0</v>
+      </c>
+      <c r="I123" s="10">
         <v>1</v>
       </c>
-      <c r="I123" s="11">
+      <c r="J123" s="11">
         <v>1020</v>
       </c>
-      <c r="J123" s="10" t="s">
+      <c r="K123" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K123" s="10" t="s">
+      <c r="L123" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="L123" s="10">
+      <c r="M123" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="124" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C124" s="8">
         <v>11406</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E124" s="8">
+      <c r="E124" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="F124" s="8">
         <v>11407</v>
       </c>
-      <c r="F124" s="10">
+      <c r="G124" s="10">
         <v>6</v>
       </c>
-      <c r="G124" s="10">
-        <v>0</v>
-      </c>
       <c r="H124" s="10">
+        <v>0</v>
+      </c>
+      <c r="I124" s="10">
         <v>0.8</v>
       </c>
-      <c r="I124" s="11">
+      <c r="J124" s="11">
         <v>1330</v>
       </c>
-      <c r="J124" s="10" t="s">
+      <c r="K124" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K124" s="10" t="s">
+      <c r="L124" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="L124" s="10">
+      <c r="M124" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="125" spans="3:12" ht="20.100000000000001" customHeight="1">
+    <row r="125" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C125" s="8">
         <v>11407</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E125" s="8">
+      <c r="E125" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="F125" s="8">
         <v>11408</v>
       </c>
-      <c r="F125" s="10">
+      <c r="G125" s="10">
         <v>7</v>
       </c>
-      <c r="G125" s="10">
-        <v>0</v>
-      </c>
       <c r="H125" s="10">
+        <v>0</v>
+      </c>
+      <c r="I125" s="10">
         <v>0.7</v>
       </c>
-      <c r="I125" s="11">
+      <c r="J125" s="11">
         <v>1680</v>
       </c>
-      <c r="J125" s="10" t="s">
+      <c r="K125" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="K125" s="10" t="s">
+      <c r="L125" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="L125" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="126" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M125" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="126" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C126" s="8">
         <v>11408</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E126" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="F126" s="8">
         <v>11409</v>
       </c>
-      <c r="F126" s="10">
+      <c r="G126" s="10">
         <v>8</v>
       </c>
-      <c r="G126" s="10">
-        <v>0</v>
-      </c>
       <c r="H126" s="10">
+        <v>0</v>
+      </c>
+      <c r="I126" s="10">
         <v>0.6</v>
       </c>
-      <c r="I126" s="11">
+      <c r="J126" s="11">
         <v>2070</v>
       </c>
-      <c r="J126" s="10" t="s">
+      <c r="K126" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="K126" s="10" t="s">
+      <c r="L126" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="L126" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="127" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M126" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="127" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C127" s="8">
         <v>11409</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E127" s="8">
+      <c r="E127" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F127" s="8">
         <v>11410</v>
       </c>
-      <c r="F127" s="10">
+      <c r="G127" s="10">
         <v>9</v>
       </c>
-      <c r="G127" s="10">
-        <v>0</v>
-      </c>
       <c r="H127" s="10">
+        <v>0</v>
+      </c>
+      <c r="I127" s="10">
         <v>0.6</v>
       </c>
-      <c r="I127" s="11">
+      <c r="J127" s="11">
         <v>2500</v>
       </c>
-      <c r="J127" s="10" t="s">
+      <c r="K127" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K127" s="10" t="s">
+      <c r="L127" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="L127" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="128" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M127" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="128" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C128" s="8">
         <v>11410</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="F128" s="8">
         <v>11411</v>
       </c>
-      <c r="F128" s="10">
+      <c r="G128" s="10">
         <v>10</v>
       </c>
-      <c r="G128" s="10">
-        <v>0</v>
-      </c>
       <c r="H128" s="10">
+        <v>0</v>
+      </c>
+      <c r="I128" s="10">
         <v>0.6</v>
       </c>
-      <c r="I128" s="11" t="s">
+      <c r="J128" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J128" s="10" t="s">
+      <c r="K128" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="K128" s="10" t="s">
+      <c r="L128" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="L128" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="129" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M128" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="129" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C129" s="8">
         <v>11411</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E129" s="8">
+      <c r="E129" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F129" s="8">
         <v>11412</v>
       </c>
-      <c r="F129" s="10">
+      <c r="G129" s="10">
         <v>11</v>
       </c>
-      <c r="G129" s="10">
-        <v>0</v>
-      </c>
       <c r="H129" s="10">
+        <v>0</v>
+      </c>
+      <c r="I129" s="10">
         <v>0.6</v>
       </c>
-      <c r="I129" s="11" t="s">
+      <c r="J129" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="J129" s="10" t="s">
+      <c r="K129" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K129" s="10" t="s">
+      <c r="L129" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="L129" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="130" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M129" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="130" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C130" s="8">
         <v>11412</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E130" s="8">
+      <c r="E130" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="F130" s="8">
         <v>11413</v>
       </c>
-      <c r="F130" s="10">
+      <c r="G130" s="10">
         <v>12</v>
       </c>
-      <c r="G130" s="10">
-        <v>0</v>
-      </c>
       <c r="H130" s="10">
+        <v>0</v>
+      </c>
+      <c r="I130" s="10">
         <v>0.6</v>
       </c>
-      <c r="I130" s="11" t="s">
+      <c r="J130" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J130" s="10" t="s">
+      <c r="K130" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="K130" s="10" t="s">
+      <c r="L130" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="L130" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="131" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M130" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="131" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C131" s="8">
         <v>11413</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="E131" s="8">
+      <c r="E131" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="F131" s="8">
         <v>11414</v>
       </c>
-      <c r="F131" s="10">
+      <c r="G131" s="10">
         <v>13</v>
       </c>
-      <c r="G131" s="10">
-        <v>0</v>
-      </c>
       <c r="H131" s="10">
+        <v>0</v>
+      </c>
+      <c r="I131" s="10">
         <v>0.6</v>
       </c>
-      <c r="I131" s="11" t="s">
+      <c r="J131" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="J131" s="10" t="s">
+      <c r="K131" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="K131" s="10" t="s">
+      <c r="L131" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="L131" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="132" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M131" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="132" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C132" s="8">
         <v>11414</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E132" s="8">
+      <c r="E132" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="F132" s="8">
         <v>11415</v>
       </c>
-      <c r="F132" s="10">
+      <c r="G132" s="10">
         <v>14</v>
       </c>
-      <c r="G132" s="10">
-        <v>0</v>
-      </c>
       <c r="H132" s="10">
+        <v>0</v>
+      </c>
+      <c r="I132" s="10">
         <v>0.6</v>
       </c>
-      <c r="I132" s="11" t="s">
+      <c r="J132" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="J132" s="10" t="s">
+      <c r="K132" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K132" s="10" t="s">
+      <c r="L132" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="L132" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="133" spans="3:12" ht="20.100000000000001" customHeight="1">
+      <c r="M132" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="133" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C133" s="8">
         <v>11415</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E133" s="8">
-        <v>0</v>
-      </c>
-      <c r="F133" s="10">
+      <c r="E133" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F133" s="8">
+        <v>0</v>
+      </c>
+      <c r="G133" s="10">
         <v>15</v>
       </c>
-      <c r="G133" s="10">
-        <v>0</v>
-      </c>
       <c r="H133" s="10">
+        <v>0</v>
+      </c>
+      <c r="I133" s="10">
         <v>0.6</v>
       </c>
-      <c r="I133" s="11" t="s">
+      <c r="J133" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="J133" s="10">
-        <v>0</v>
-      </c>
-      <c r="K133" s="10" t="s">
+      <c r="K133" s="10">
+        <v>0</v>
+      </c>
+      <c r="L133" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="L133" s="10">
+      <c r="M133" s="10">
         <v>0.04</v>
       </c>
     </row>

--- a/Excel/UnionQiangHuaConfig.xlsx
+++ b/Excel/UnionQiangHuaConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A99A114-E89C-42A5-A26B-262C826266E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D0BE67-5F8A-4833-A2CB-4931E1538853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1270,7 +1270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="489">
   <si>
     <t>Id</t>
   </si>
@@ -1434,13 +1434,7 @@
     <t>生命修炼2级</t>
   </si>
   <si>
-    <t>100203;600</t>
-  </si>
-  <si>
     <t>生命修炼3级</t>
-  </si>
-  <si>
-    <t>100203;1200</t>
   </si>
   <si>
     <t>生命修炼4级</t>
@@ -2553,6 +2547,246 @@
   </si>
   <si>
     <t>Pet Magic Defense Level 15</t>
+  </si>
+  <si>
+    <t>攻击修炼16级</t>
+  </si>
+  <si>
+    <t>攻击修炼17级</t>
+  </si>
+  <si>
+    <t>攻击修炼18级</t>
+  </si>
+  <si>
+    <t>攻击修炼19级</t>
+  </si>
+  <si>
+    <t>攻击修炼20级</t>
+  </si>
+  <si>
+    <t>Attack Training Level 16</t>
+  </si>
+  <si>
+    <t>Attack Training Level 17</t>
+  </si>
+  <si>
+    <t>Attack Training Level 18</t>
+  </si>
+  <si>
+    <t>Attack Training Level 19</t>
+  </si>
+  <si>
+    <t>Attack Training Level 20</t>
+  </si>
+  <si>
+    <t>12500</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>17500</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>22500</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>100403;3600</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100403;3900</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100403;4200</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100403;4500</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100403;4800</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000163;600</t>
+  </si>
+  <si>
+    <t>10000163;700</t>
+  </si>
+  <si>
+    <t>10000163;800</t>
+  </si>
+  <si>
+    <t>10000163;900</t>
+  </si>
+  <si>
+    <t>10000163;1000</t>
+  </si>
+  <si>
+    <t>10000163;1200</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命修炼16级</t>
+  </si>
+  <si>
+    <t>生命修炼17级</t>
+  </si>
+  <si>
+    <t>生命修炼18级</t>
+  </si>
+  <si>
+    <t>生命修炼19级</t>
+  </si>
+  <si>
+    <t>生命修炼20级</t>
+  </si>
+  <si>
+    <t>Life Training Level 16</t>
+  </si>
+  <si>
+    <t>Life Training Level 17</t>
+  </si>
+  <si>
+    <t>Life Training Level 18</t>
+  </si>
+  <si>
+    <t>Life Training Level 19</t>
+  </si>
+  <si>
+    <t>Life Training Level 20</t>
+  </si>
+  <si>
+    <t>防御修炼16级</t>
+  </si>
+  <si>
+    <t>防御修炼17级</t>
+  </si>
+  <si>
+    <t>防御修炼18级</t>
+  </si>
+  <si>
+    <t>防御修炼19级</t>
+  </si>
+  <si>
+    <t>防御修炼20级</t>
+  </si>
+  <si>
+    <t>Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>Defense Training Level 20</t>
+  </si>
+  <si>
+    <t>法防修炼16级</t>
+  </si>
+  <si>
+    <t>法防修炼17级</t>
+  </si>
+  <si>
+    <t>法防修炼18级</t>
+  </si>
+  <si>
+    <t>法防修炼19级</t>
+  </si>
+  <si>
+    <t>法防修炼20级</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 16</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 17</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 18</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 19</t>
+  </si>
+  <si>
+    <t>Magic Defense Training Level 20</t>
+  </si>
+  <si>
+    <t>100803;3600</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100803;3900</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100803;4200</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100803;4500</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100803;4800</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100603;3600</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100603;3900</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100603;4200</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100603;4500</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100603;4800</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100203;600</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100203;1200</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>100203;21600</t>
+  </si>
+  <si>
+    <t>100203;23400</t>
+  </si>
+  <si>
+    <t>100203;25200</t>
+  </si>
+  <si>
+    <t>100203;27000</t>
+  </si>
+  <si>
+    <t>100203;28800</t>
   </si>
 </sst>
 </file>
@@ -2757,7 +2991,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2785,6 +3019,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3943,7 +4180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:IE133"/>
+  <dimension ref="C1:IE153"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="8.5" style="2" customWidth="1"/>
@@ -3959,7 +4196,7 @@
     <row r="2" spans="3:239" ht="13.5" customHeight="1">
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="3:239" ht="20.100000000000001" customHeight="1">
@@ -4005,7 +4242,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>11</v>
@@ -4075,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F6" s="8">
         <v>10101</v>
@@ -4106,7 +4343,7 @@
         <v>23</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F7" s="8">
         <v>10102</v>
@@ -4139,7 +4376,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F8" s="8">
         <v>10103</v>
@@ -4173,7 +4410,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F9" s="8">
         <v>10104</v>
@@ -4207,7 +4444,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F10" s="8">
         <v>10105</v>
@@ -4241,7 +4478,7 @@
         <v>31</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F11" s="8">
         <v>10106</v>
@@ -4274,7 +4511,7 @@
         <v>33</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F12" s="8">
         <v>10107</v>
@@ -4308,7 +4545,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F13" s="8">
         <v>10108</v>
@@ -4342,7 +4579,7 @@
         <v>37</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F14" s="8">
         <v>10109</v>
@@ -4376,7 +4613,7 @@
         <v>39</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F15" s="8">
         <v>10110</v>
@@ -4410,7 +4647,7 @@
         <v>41</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F16" s="8">
         <v>10111</v>
@@ -4444,7 +4681,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F17" s="8">
         <v>10112</v>
@@ -4478,7 +4715,7 @@
         <v>47</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F18" s="8">
         <v>10113</v>
@@ -4493,10 +4730,10 @@
         <v>0.5</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>49</v>
@@ -4511,10 +4748,10 @@
         <v>10113</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F19" s="8">
         <v>10114</v>
@@ -4529,13 +4766,13 @@
         <v>0.5</v>
       </c>
       <c r="J19" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="M19" s="10">
         <v>0.04</v>
@@ -4547,10 +4784,10 @@
         <v>10114</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F20" s="8">
         <v>10115</v>
@@ -4565,13 +4802,13 @@
         <v>0.5</v>
       </c>
       <c r="J20" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>243</v>
       </c>
       <c r="M20" s="10">
         <v>0.04</v>
@@ -4583,13 +4820,13 @@
         <v>10115</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F21" s="8">
-        <v>0</v>
+        <v>10116</v>
       </c>
       <c r="G21" s="10">
         <v>15</v>
@@ -4601,198 +4838,214 @@
         <v>0.5</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K21" s="10"/>
+        <v>425</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>436</v>
+      </c>
       <c r="L21" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M21" s="10">
         <v>0.04</v>
       </c>
       <c r="IE21"/>
     </row>
-    <row r="22" spans="3:239" ht="22.5" customHeight="1">
+    <row r="22" spans="3:239" ht="19.5" customHeight="1">
       <c r="C22" s="8">
-        <v>10200</v>
+        <v>10116</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>50</v>
+        <v>415</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>312</v>
+        <v>420</v>
       </c>
       <c r="F22" s="8">
-        <v>10201</v>
+        <v>10117</v>
       </c>
       <c r="G22" s="10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H22" s="10">
         <v>0</v>
       </c>
       <c r="I22" s="10">
-        <v>1</v>
-      </c>
-      <c r="J22" s="11">
-        <v>100</v>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+        <v>0.45</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>431</v>
+      </c>
       <c r="M22" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="23" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.03</v>
+      </c>
+      <c r="IE22"/>
+    </row>
+    <row r="23" spans="3:239" ht="19.5" customHeight="1">
       <c r="C23" s="8">
-        <v>10201</v>
+        <v>10117</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>51</v>
+        <v>416</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>313</v>
+        <v>421</v>
       </c>
       <c r="F23" s="8">
-        <v>10202</v>
+        <v>10118</v>
       </c>
       <c r="G23" s="10">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H23" s="10">
         <v>0</v>
       </c>
       <c r="I23" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J23" s="11">
-        <v>220</v>
-      </c>
-      <c r="K23" s="10"/>
+        <v>0.4</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>438</v>
+      </c>
       <c r="L23" s="10" t="s">
-        <v>52</v>
+        <v>432</v>
       </c>
       <c r="M23" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.03</v>
+      </c>
+      <c r="IE23"/>
+    </row>
+    <row r="24" spans="3:239" ht="19.5" customHeight="1">
       <c r="C24" s="8">
-        <v>10202</v>
+        <v>10118</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>53</v>
+        <v>417</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>314</v>
+        <v>422</v>
       </c>
       <c r="F24" s="8">
-        <v>10203</v>
+        <v>10119</v>
       </c>
       <c r="G24" s="10">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
       </c>
       <c r="I24" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J24" s="11">
-        <v>375</v>
-      </c>
-      <c r="K24" s="10"/>
+        <v>0.35</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>439</v>
+      </c>
       <c r="L24" s="10" t="s">
-        <v>54</v>
+        <v>433</v>
       </c>
       <c r="M24" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE24"/>
     </row>
     <row r="25" spans="3:239" ht="19.5" customHeight="1">
       <c r="C25" s="8">
-        <v>10203</v>
+        <v>10119</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>55</v>
+        <v>418</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>289</v>
+        <v>423</v>
       </c>
       <c r="F25" s="8">
-        <v>10204</v>
+        <v>10120</v>
       </c>
       <c r="G25" s="10">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
       </c>
       <c r="I25" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J25" s="11">
-        <v>560</v>
-      </c>
-      <c r="K25" s="10"/>
+        <v>0.3</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>440</v>
+      </c>
       <c r="L25" s="10" t="s">
-        <v>56</v>
+        <v>434</v>
       </c>
       <c r="M25" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE25"/>
     </row>
     <row r="26" spans="3:239" ht="19.5" customHeight="1">
       <c r="C26" s="8">
-        <v>10204</v>
+        <v>10120</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>57</v>
+        <v>419</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="F26" s="8">
-        <v>10205</v>
+        <v>0</v>
       </c>
       <c r="G26" s="10">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H26" s="10">
         <v>0</v>
       </c>
       <c r="I26" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J26" s="11">
-        <v>775</v>
-      </c>
-      <c r="K26" s="10"/>
+        <v>0.3</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>441</v>
+      </c>
       <c r="L26" s="10" t="s">
-        <v>58</v>
+        <v>435</v>
       </c>
       <c r="M26" s="10">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="IE26"/>
     </row>
     <row r="27" spans="3:239" ht="22.5" customHeight="1">
       <c r="C27" s="8">
-        <v>10205</v>
+        <v>10200</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="F27" s="8">
-        <v>10206</v>
+        <v>10201</v>
       </c>
       <c r="G27" s="10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="10">
         <v>0</v>
@@ -4801,31 +5054,29 @@
         <v>1</v>
       </c>
       <c r="J27" s="11">
-        <v>1020</v>
+        <v>100</v>
       </c>
       <c r="K27" s="10"/>
-      <c r="L27" s="10" t="s">
-        <v>60</v>
-      </c>
+      <c r="L27" s="10"/>
       <c r="M27" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C28" s="8">
-        <v>10206</v>
+        <v>10201</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F28" s="8">
-        <v>10207</v>
+        <v>10202</v>
       </c>
       <c r="G28" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -4834,11 +5085,11 @@
         <v>0.8</v>
       </c>
       <c r="J28" s="11">
-        <v>1330</v>
+        <v>220</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M28" s="10">
         <v>0.05</v>
@@ -4846,19 +5097,19 @@
     </row>
     <row r="29" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C29" s="8">
-        <v>10207</v>
+        <v>10202</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F29" s="8">
-        <v>10208</v>
+        <v>10203</v>
       </c>
       <c r="G29" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H29" s="10">
         <v>0</v>
@@ -4867,11 +5118,11 @@
         <v>0.7</v>
       </c>
       <c r="J29" s="11">
-        <v>1680</v>
+        <v>375</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10" t="s">
-        <v>64</v>
+        <v>482</v>
       </c>
       <c r="M29" s="10">
         <v>0.04</v>
@@ -4880,19 +5131,19 @@
     </row>
     <row r="30" spans="3:239" ht="19.5" customHeight="1">
       <c r="C30" s="8">
-        <v>10208</v>
+        <v>10203</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="F30" s="8">
-        <v>10209</v>
+        <v>10204</v>
       </c>
       <c r="G30" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H30" s="10">
         <v>0</v>
@@ -4901,11 +5152,11 @@
         <v>0.6</v>
       </c>
       <c r="J30" s="11">
-        <v>2070</v>
+        <v>560</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10" t="s">
-        <v>66</v>
+        <v>483</v>
       </c>
       <c r="M30" s="10">
         <v>0.04</v>
@@ -4914,19 +5165,19 @@
     </row>
     <row r="31" spans="3:239" ht="19.5" customHeight="1">
       <c r="C31" s="8">
-        <v>10209</v>
+        <v>10204</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F31" s="8">
-        <v>10210</v>
+        <v>10205</v>
       </c>
       <c r="G31" s="10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
@@ -4935,679 +5186,690 @@
         <v>0.6</v>
       </c>
       <c r="J31" s="11">
-        <v>2500</v>
+        <v>775</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="10" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="M31" s="10">
         <v>0.04</v>
       </c>
       <c r="IE31"/>
     </row>
-    <row r="32" spans="3:239" ht="19.5" customHeight="1">
+    <row r="32" spans="3:239" ht="22.5" customHeight="1">
       <c r="C32" s="8">
-        <v>10210</v>
+        <v>10205</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F32" s="8">
-        <v>10211</v>
+        <v>10206</v>
       </c>
       <c r="G32" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H32" s="10">
         <v>0</v>
       </c>
       <c r="I32" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="J32" s="11">
+        <v>1020</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M32" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE32"/>
-    </row>
-    <row r="33" spans="3:239" ht="19.5" customHeight="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C33" s="8">
-        <v>10211</v>
+        <v>10206</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F33" s="8">
-        <v>10212</v>
+        <v>10207</v>
       </c>
       <c r="G33" s="10">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H33" s="10">
         <v>0</v>
       </c>
       <c r="I33" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>45</v>
+        <v>0.8</v>
+      </c>
+      <c r="J33" s="11">
+        <v>1330</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="10" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="M33" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="N33" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="C34" s="8">
+        <v>10207</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="F34" s="8">
+        <v>10208</v>
+      </c>
+      <c r="G34" s="10">
+        <v>7</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J34" s="11">
+        <v>1680</v>
+      </c>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE34"/>
+    </row>
+    <row r="35" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C35" s="8">
+        <v>10208</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="F35" s="8">
+        <v>10209</v>
+      </c>
+      <c r="G35" s="10">
+        <v>8</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="11">
+        <v>2070</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE35"/>
+    </row>
+    <row r="36" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C36" s="8">
+        <v>10209</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="F36" s="8">
+        <v>10210</v>
+      </c>
+      <c r="G36" s="10">
+        <v>9</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J36" s="11">
+        <v>2500</v>
+      </c>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M36" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE36"/>
+    </row>
+    <row r="37" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C37" s="8">
+        <v>10210</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="F37" s="8">
+        <v>10211</v>
+      </c>
+      <c r="G37" s="10">
+        <v>10</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M37" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="IE37"/>
+    </row>
+    <row r="38" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C38" s="8">
+        <v>10211</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F38" s="8">
+        <v>10212</v>
+      </c>
+      <c r="G38" s="10">
+        <v>11</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="M38" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N38" s="13">
         <f>14400-12600</f>
         <v>1800</v>
       </c>
-      <c r="IE33"/>
-    </row>
-    <row r="34" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C34" s="8">
+      <c r="IE38"/>
+    </row>
+    <row r="39" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C39" s="8">
         <v>10212</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E34" s="12" t="s">
+      <c r="D39" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F39" s="8">
+        <v>10213</v>
+      </c>
+      <c r="G39" s="10">
+        <v>12</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0</v>
+      </c>
+      <c r="I39" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N39" s="13">
+        <v>14400</v>
+      </c>
+      <c r="IE39"/>
+    </row>
+    <row r="40" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C40" s="8">
+        <v>10213</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="F40" s="8">
+        <v>10214</v>
+      </c>
+      <c r="G40" s="10">
+        <v>13</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0</v>
+      </c>
+      <c r="I40" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="M40" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N40" s="13">
+        <f>N39+$N$38</f>
+        <v>16200</v>
+      </c>
+      <c r="IE40"/>
+    </row>
+    <row r="41" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C41" s="8">
+        <v>10214</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="F34" s="8">
-        <v>10213</v>
-      </c>
-      <c r="G34" s="10">
-        <v>12</v>
-      </c>
-      <c r="H34" s="10">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10">
+      <c r="F41" s="8">
+        <v>10215</v>
+      </c>
+      <c r="G41" s="10">
+        <v>14</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0</v>
+      </c>
+      <c r="I41" s="10">
         <v>0.6</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="J41" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K41" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="L34" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="M34" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="N34" s="2">
-        <v>14400</v>
-      </c>
-      <c r="IE34"/>
-    </row>
-    <row r="35" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C35" s="8">
-        <v>10213</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="L41" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="M41" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N41" s="13">
+        <f t="shared" ref="N41:N42" si="0">N40+$N$38</f>
+        <v>18000</v>
+      </c>
+      <c r="IE41"/>
+    </row>
+    <row r="42" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C42" s="8">
+        <v>10215</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E42" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="F35" s="8">
-        <v>10214</v>
-      </c>
-      <c r="G35" s="10">
-        <v>13</v>
-      </c>
-      <c r="H35" s="10">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10">
+      <c r="F42" s="8">
+        <v>10216</v>
+      </c>
+      <c r="G42" s="10">
+        <v>15</v>
+      </c>
+      <c r="H42" s="10">
+        <v>0</v>
+      </c>
+      <c r="I42" s="10">
         <v>0.6</v>
       </c>
-      <c r="J35" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="L35" s="10" t="s">
+      <c r="J42" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="L42" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="M35" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="N35" s="2">
-        <f>N34+$N$33</f>
-        <v>16200</v>
-      </c>
-      <c r="IE35"/>
-    </row>
-    <row r="36" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C36" s="8">
-        <v>10214</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="F36" s="8">
-        <v>10215</v>
-      </c>
-      <c r="G36" s="10">
-        <v>14</v>
-      </c>
-      <c r="H36" s="10">
-        <v>0</v>
-      </c>
-      <c r="I36" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="M36" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="N36" s="2">
-        <f t="shared" ref="N36:N37" si="0">N35+$N$33</f>
-        <v>18000</v>
-      </c>
-      <c r="IE36"/>
-    </row>
-    <row r="37" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C37" s="8">
-        <v>10215</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="F37" s="8">
-        <v>0</v>
-      </c>
-      <c r="G37" s="10">
-        <v>15</v>
-      </c>
-      <c r="H37" s="10">
-        <v>0</v>
-      </c>
-      <c r="I37" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="M37" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="N37" s="2">
+      <c r="M42" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="N42" s="13">
         <f t="shared" si="0"/>
         <v>19800</v>
       </c>
-      <c r="IE37"/>
-    </row>
-    <row r="38" spans="3:239" ht="22.5" customHeight="1">
-      <c r="C38" s="8">
-        <v>10300</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="F38" s="8">
-        <v>10301</v>
-      </c>
-      <c r="G38" s="10">
-        <v>0</v>
-      </c>
-      <c r="H38" s="10">
-        <v>0</v>
-      </c>
-      <c r="I38" s="10">
-        <v>1</v>
-      </c>
-      <c r="J38" s="11">
-        <v>100</v>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="3:239" ht="20.100000000000001" customHeight="1">
-      <c r="C39" s="8">
-        <v>10301</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="F39" s="8">
-        <v>10302</v>
-      </c>
-      <c r="G39" s="10">
-        <v>1</v>
-      </c>
-      <c r="H39" s="10">
-        <v>0</v>
-      </c>
-      <c r="I39" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J39" s="11">
-        <v>220</v>
-      </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M39" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="40" spans="3:239" ht="20.100000000000001" customHeight="1">
-      <c r="C40" s="8">
-        <v>10302</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="F40" s="8">
-        <v>10303</v>
-      </c>
-      <c r="G40" s="10">
-        <v>2</v>
-      </c>
-      <c r="H40" s="10">
-        <v>0</v>
-      </c>
-      <c r="I40" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J40" s="11">
-        <v>375</v>
-      </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M40" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE40"/>
-    </row>
-    <row r="41" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C41" s="8">
-        <v>10303</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="F41" s="8">
-        <v>10304</v>
-      </c>
-      <c r="G41" s="10">
-        <v>3</v>
-      </c>
-      <c r="H41" s="10">
-        <v>0</v>
-      </c>
-      <c r="I41" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J41" s="11">
-        <v>560</v>
-      </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="M41" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE41"/>
-    </row>
-    <row r="42" spans="3:239" ht="19.5" customHeight="1">
-      <c r="C42" s="8">
-        <v>10304</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="F42" s="8">
-        <v>10305</v>
-      </c>
-      <c r="G42" s="10">
-        <v>4</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-      <c r="I42" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J42" s="11">
-        <v>775</v>
-      </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="M42" s="10">
-        <v>0.04</v>
-      </c>
       <c r="IE42"/>
     </row>
-    <row r="43" spans="3:239" ht="20.100000000000001" customHeight="1">
+    <row r="43" spans="3:239" ht="19.5" customHeight="1">
       <c r="C43" s="8">
-        <v>10305</v>
+        <v>10216</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>293</v>
+        <v>447</v>
       </c>
       <c r="F43" s="8">
-        <v>10306</v>
+        <v>10217</v>
       </c>
       <c r="G43" s="10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H43" s="10">
         <v>0</v>
       </c>
       <c r="I43" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J43" s="11">
-        <v>1020</v>
-      </c>
-      <c r="K43" s="10"/>
+        <v>0.45</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>437</v>
+      </c>
       <c r="L43" s="10" t="s">
-        <v>85</v>
+        <v>484</v>
       </c>
       <c r="M43" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="44" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.03</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="IE43"/>
+    </row>
+    <row r="44" spans="3:239" ht="19.5" customHeight="1">
       <c r="C44" s="8">
-        <v>10306</v>
+        <v>10217</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>86</v>
+        <v>443</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>329</v>
+        <v>448</v>
       </c>
       <c r="F44" s="8">
-        <v>10307</v>
+        <v>10218</v>
       </c>
       <c r="G44" s="10">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H44" s="10">
         <v>0</v>
       </c>
       <c r="I44" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J44" s="11">
-        <v>1330</v>
-      </c>
-      <c r="K44" s="10"/>
+        <v>0.4</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>438</v>
+      </c>
       <c r="L44" s="10" t="s">
-        <v>87</v>
+        <v>485</v>
       </c>
       <c r="M44" s="10">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="IE44"/>
     </row>
     <row r="45" spans="3:239" ht="19.5" customHeight="1">
       <c r="C45" s="8">
-        <v>10307</v>
+        <v>10218</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>88</v>
+        <v>444</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>330</v>
+        <v>449</v>
       </c>
       <c r="F45" s="8">
-        <v>10308</v>
+        <v>10219</v>
       </c>
       <c r="G45" s="10">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H45" s="10">
         <v>0</v>
       </c>
       <c r="I45" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J45" s="11">
-        <v>1680</v>
-      </c>
-      <c r="K45" s="10"/>
+        <v>0.35</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>439</v>
+      </c>
       <c r="L45" s="10" t="s">
-        <v>89</v>
+        <v>486</v>
       </c>
       <c r="M45" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE45"/>
     </row>
     <row r="46" spans="3:239" ht="19.5" customHeight="1">
       <c r="C46" s="8">
-        <v>10308</v>
+        <v>10219</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>90</v>
+        <v>445</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>294</v>
+        <v>450</v>
       </c>
       <c r="F46" s="8">
-        <v>10309</v>
+        <v>10220</v>
       </c>
       <c r="G46" s="10">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H46" s="10">
         <v>0</v>
       </c>
       <c r="I46" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J46" s="11">
-        <v>2070</v>
-      </c>
-      <c r="K46" s="10"/>
+        <v>0.3</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>440</v>
+      </c>
       <c r="L46" s="10" t="s">
-        <v>91</v>
+        <v>487</v>
       </c>
       <c r="M46" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE46"/>
     </row>
     <row r="47" spans="3:239" ht="19.5" customHeight="1">
       <c r="C47" s="8">
-        <v>10309</v>
+        <v>10220</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>92</v>
+        <v>446</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>331</v>
+        <v>451</v>
       </c>
       <c r="F47" s="8">
-        <v>10310</v>
+        <v>0</v>
       </c>
       <c r="G47" s="10">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H47" s="10">
         <v>0</v>
       </c>
       <c r="I47" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J47" s="11">
-        <v>2500</v>
-      </c>
-      <c r="K47" s="10"/>
+        <v>0.3</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>441</v>
+      </c>
       <c r="L47" s="10" t="s">
-        <v>93</v>
+        <v>488</v>
       </c>
       <c r="M47" s="10">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="IE47"/>
     </row>
-    <row r="48" spans="3:239" ht="19.5" customHeight="1">
+    <row r="48" spans="3:239" ht="22.5" customHeight="1">
       <c r="C48" s="8">
-        <v>10310</v>
+        <v>10300</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>332</v>
+        <v>288</v>
       </c>
       <c r="F48" s="8">
-        <v>10311</v>
+        <v>10301</v>
       </c>
       <c r="G48" s="10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H48" s="10">
         <v>0</v>
       </c>
       <c r="I48" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="J48" s="11">
+        <v>100</v>
       </c>
       <c r="K48" s="10"/>
-      <c r="L48" s="10" t="s">
-        <v>95</v>
-      </c>
+      <c r="L48" s="10"/>
       <c r="M48" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE48"/>
-    </row>
-    <row r="49" spans="3:239" ht="19.5" customHeight="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="49" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C49" s="8">
-        <v>10311</v>
+        <v>10301</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="F49" s="8">
-        <v>10312</v>
+        <v>10302</v>
       </c>
       <c r="G49" s="10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H49" s="10">
         <v>0</v>
       </c>
       <c r="I49" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>45</v>
+        <v>0.8</v>
+      </c>
+      <c r="J49" s="11">
+        <v>220</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="M49" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE49"/>
-    </row>
-    <row r="50" spans="3:239" ht="19.5" customHeight="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C50" s="8">
-        <v>10312</v>
+        <v>10302</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="F50" s="8">
-        <v>10313</v>
+        <v>10303</v>
       </c>
       <c r="G50" s="10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H50" s="10">
         <v>0</v>
       </c>
       <c r="I50" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="K50" s="10" t="s">
-        <v>266</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="J50" s="11">
+        <v>375</v>
+      </c>
+      <c r="K50" s="10"/>
       <c r="L50" s="10" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="M50" s="10">
         <v>0.04</v>
@@ -5616,19 +5878,19 @@
     </row>
     <row r="51" spans="3:239" ht="19.5" customHeight="1">
       <c r="C51" s="8">
-        <v>10313</v>
+        <v>10303</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F51" s="8">
-        <v>10314</v>
+        <v>10304</v>
       </c>
       <c r="G51" s="10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H51" s="10">
         <v>0</v>
@@ -5636,14 +5898,12 @@
       <c r="I51" s="10">
         <v>0.6</v>
       </c>
-      <c r="J51" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K51" s="10" t="s">
-        <v>267</v>
-      </c>
+      <c r="J51" s="11">
+        <v>560</v>
+      </c>
+      <c r="K51" s="10"/>
       <c r="L51" s="10" t="s">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="M51" s="10">
         <v>0.04</v>
@@ -5652,19 +5912,19 @@
     </row>
     <row r="52" spans="3:239" ht="19.5" customHeight="1">
       <c r="C52" s="8">
-        <v>10314</v>
+        <v>10304</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="F52" s="8">
-        <v>10315</v>
+        <v>10305</v>
       </c>
       <c r="G52" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H52" s="10">
         <v>0</v>
@@ -5672,146 +5932,147 @@
       <c r="I52" s="10">
         <v>0.6</v>
       </c>
-      <c r="J52" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>268</v>
-      </c>
+      <c r="J52" s="11">
+        <v>775</v>
+      </c>
+      <c r="K52" s="10"/>
       <c r="L52" s="10" t="s">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="M52" s="10">
         <v>0.04</v>
       </c>
       <c r="IE52"/>
     </row>
-    <row r="53" spans="3:239" ht="19.5" customHeight="1">
+    <row r="53" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C53" s="8">
-        <v>10315</v>
+        <v>10305</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>10306</v>
       </c>
       <c r="G53" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H53" s="10">
         <v>0</v>
       </c>
       <c r="I53" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>48</v>
+        <v>0.8</v>
+      </c>
+      <c r="J53" s="11">
+        <v>1020</v>
       </c>
       <c r="K53" s="10"/>
       <c r="L53" s="10" t="s">
-        <v>256</v>
+        <v>83</v>
       </c>
       <c r="M53" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE53"/>
-    </row>
-    <row r="54" spans="3:239" ht="22.5" customHeight="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="54" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C54" s="8">
-        <v>10400</v>
+        <v>10306</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F54" s="8">
-        <v>10401</v>
+        <v>10307</v>
       </c>
       <c r="G54" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H54" s="10">
         <v>0</v>
       </c>
       <c r="I54" s="10">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" s="11">
-        <v>100</v>
+        <v>1330</v>
       </c>
       <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
+      <c r="L54" s="10" t="s">
+        <v>85</v>
+      </c>
       <c r="M54" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="55" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+      <c r="IE54"/>
+    </row>
+    <row r="55" spans="3:239" ht="19.5" customHeight="1">
       <c r="C55" s="8">
-        <v>10401</v>
+        <v>10307</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="F55" s="8">
-        <v>10402</v>
+        <v>10308</v>
       </c>
       <c r="G55" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H55" s="10">
         <v>0</v>
       </c>
       <c r="I55" s="10">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J55" s="11">
-        <v>220</v>
+        <v>1680</v>
       </c>
       <c r="K55" s="10"/>
       <c r="L55" s="10" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="M55" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="56" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+      <c r="IE55"/>
+    </row>
+    <row r="56" spans="3:239" ht="19.5" customHeight="1">
       <c r="C56" s="8">
-        <v>10402</v>
+        <v>10308</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="F56" s="8">
-        <v>10403</v>
+        <v>10309</v>
       </c>
       <c r="G56" s="10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H56" s="10">
         <v>0</v>
       </c>
       <c r="I56" s="10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J56" s="11">
-        <v>375</v>
+        <v>2070</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="10" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="M56" s="10">
         <v>0.04</v>
@@ -5820,19 +6081,19 @@
     </row>
     <row r="57" spans="3:239" ht="19.5" customHeight="1">
       <c r="C57" s="8">
-        <v>10403</v>
+        <v>10309</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="F57" s="8">
-        <v>10404</v>
+        <v>10310</v>
       </c>
       <c r="G57" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H57" s="10">
         <v>0</v>
@@ -5841,11 +6102,11 @@
         <v>0.6</v>
       </c>
       <c r="J57" s="11">
-        <v>560</v>
+        <v>2500</v>
       </c>
       <c r="K57" s="10"/>
       <c r="L57" s="10" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="M57" s="10">
         <v>0.04</v>
@@ -5854,19 +6115,19 @@
     </row>
     <row r="58" spans="3:239" ht="19.5" customHeight="1">
       <c r="C58" s="8">
-        <v>10404</v>
+        <v>10310</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="F58" s="8">
-        <v>10405</v>
+        <v>10311</v>
       </c>
       <c r="G58" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H58" s="10">
         <v>0</v>
@@ -5874,112 +6135,118 @@
       <c r="I58" s="10">
         <v>0.6</v>
       </c>
-      <c r="J58" s="11">
-        <v>775</v>
+      <c r="J58" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="K58" s="10"/>
       <c r="L58" s="10" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="M58" s="10">
         <v>0.04</v>
       </c>
       <c r="IE58"/>
     </row>
-    <row r="59" spans="3:239" ht="22.5" customHeight="1">
+    <row r="59" spans="3:239" ht="19.5" customHeight="1">
       <c r="C59" s="8">
-        <v>10405</v>
+        <v>10311</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="F59" s="8">
-        <v>10406</v>
+        <v>10312</v>
       </c>
       <c r="G59" s="10">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H59" s="10">
         <v>0</v>
       </c>
       <c r="I59" s="10">
-        <v>1</v>
-      </c>
-      <c r="J59" s="11">
-        <v>1020</v>
+        <v>0.6</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="K59" s="10"/>
       <c r="L59" s="10" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="M59" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="60" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+      <c r="IE59"/>
+    </row>
+    <row r="60" spans="3:239" ht="19.5" customHeight="1">
       <c r="C60" s="8">
-        <v>10406</v>
+        <v>10312</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="F60" s="8">
-        <v>10407</v>
+        <v>10313</v>
       </c>
       <c r="G60" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H60" s="10">
         <v>0</v>
       </c>
       <c r="I60" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J60" s="11">
-        <v>1330</v>
-      </c>
-      <c r="K60" s="10"/>
+        <v>0.6</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="L60" s="10" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="M60" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="61" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+      <c r="IE60"/>
+    </row>
+    <row r="61" spans="3:239" ht="19.5" customHeight="1">
       <c r="C61" s="8">
-        <v>10407</v>
+        <v>10313</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>113</v>
+        <v>249</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="F61" s="8">
-        <v>10408</v>
+        <v>10314</v>
       </c>
       <c r="G61" s="10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H61" s="10">
         <v>0</v>
       </c>
       <c r="I61" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J61" s="11">
-        <v>1680</v>
-      </c>
-      <c r="K61" s="10"/>
+        <v>0.6</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="L61" s="10" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="M61" s="10">
         <v>0.04</v>
@@ -5988,19 +6255,19 @@
     </row>
     <row r="62" spans="3:239" ht="19.5" customHeight="1">
       <c r="C62" s="8">
-        <v>10408</v>
+        <v>10314</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>115</v>
+        <v>250</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="F62" s="8">
-        <v>10409</v>
+        <v>10315</v>
       </c>
       <c r="G62" s="10">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H62" s="10">
         <v>0</v>
@@ -6008,12 +6275,14 @@
       <c r="I62" s="10">
         <v>0.6</v>
       </c>
-      <c r="J62" s="11">
-        <v>2070</v>
-      </c>
-      <c r="K62" s="10"/>
+      <c r="J62" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="L62" s="10" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="M62" s="10">
         <v>0.04</v>
@@ -6022,19 +6291,19 @@
     </row>
     <row r="63" spans="3:239" ht="19.5" customHeight="1">
       <c r="C63" s="8">
-        <v>10409</v>
+        <v>10315</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>117</v>
+        <v>251</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
       <c r="F63" s="8">
-        <v>10410</v>
+        <v>10316</v>
       </c>
       <c r="G63" s="10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H63" s="10">
         <v>0</v>
@@ -6042,12 +6311,14 @@
       <c r="I63" s="10">
         <v>0.6</v>
       </c>
-      <c r="J63" s="11">
-        <v>2500</v>
-      </c>
-      <c r="K63" s="10"/>
+      <c r="J63" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>436</v>
+      </c>
       <c r="L63" s="10" t="s">
-        <v>118</v>
+        <v>254</v>
       </c>
       <c r="M63" s="10">
         <v>0.04</v>
@@ -6056,332 +6327,331 @@
     </row>
     <row r="64" spans="3:239" ht="19.5" customHeight="1">
       <c r="C64" s="8">
-        <v>10410</v>
+        <v>10316</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>119</v>
+        <v>452</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>346</v>
+        <v>457</v>
       </c>
       <c r="F64" s="8">
-        <v>10411</v>
+        <v>10317</v>
       </c>
       <c r="G64" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H64" s="10">
         <v>0</v>
       </c>
       <c r="I64" s="10">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="K64" s="10"/>
+        <v>426</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>437</v>
+      </c>
       <c r="L64" s="10" t="s">
-        <v>120</v>
+        <v>477</v>
       </c>
       <c r="M64" s="10">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="IE64"/>
     </row>
     <row r="65" spans="3:239" ht="19.5" customHeight="1">
       <c r="C65" s="8">
-        <v>10411</v>
+        <v>10317</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>121</v>
+        <v>453</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>347</v>
+        <v>458</v>
       </c>
       <c r="F65" s="8">
-        <v>10412</v>
+        <v>10318</v>
       </c>
       <c r="G65" s="10">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H65" s="10">
         <v>0</v>
       </c>
       <c r="I65" s="10">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K65" s="10"/>
+        <v>427</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>438</v>
+      </c>
       <c r="L65" s="10" t="s">
-        <v>122</v>
+        <v>478</v>
       </c>
       <c r="M65" s="10">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="IE65"/>
     </row>
     <row r="66" spans="3:239" ht="19.5" customHeight="1">
       <c r="C66" s="8">
-        <v>10412</v>
+        <v>10318</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>123</v>
+        <v>454</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>348</v>
+        <v>459</v>
       </c>
       <c r="F66" s="8">
-        <v>10413</v>
+        <v>10319</v>
       </c>
       <c r="G66" s="10">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H66" s="10">
         <v>0</v>
       </c>
       <c r="I66" s="10">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>239</v>
+        <v>428</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>266</v>
+        <v>439</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>124</v>
+        <v>479</v>
       </c>
       <c r="M66" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE66"/>
     </row>
     <row r="67" spans="3:239" ht="19.5" customHeight="1">
       <c r="C67" s="8">
-        <v>10413</v>
+        <v>10319</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>257</v>
+        <v>455</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>349</v>
+        <v>460</v>
       </c>
       <c r="F67" s="8">
-        <v>10414</v>
+        <v>10320</v>
       </c>
       <c r="G67" s="10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H67" s="10">
         <v>0</v>
       </c>
       <c r="I67" s="10">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>240</v>
+        <v>429</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>267</v>
+        <v>440</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="M67" s="10">
-        <v>0.04</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="IE67"/>
     </row>
     <row r="68" spans="3:239" ht="19.5" customHeight="1">
       <c r="C68" s="8">
-        <v>10414</v>
+        <v>10320</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>258</v>
+        <v>456</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>350</v>
+        <v>461</v>
       </c>
       <c r="F68" s="8">
-        <v>10415</v>
+        <v>0</v>
       </c>
       <c r="G68" s="10">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H68" s="10">
         <v>0</v>
       </c>
       <c r="I68" s="10">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>241</v>
+        <v>430</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>268</v>
+        <v>441</v>
       </c>
       <c r="L68" s="10" t="s">
-        <v>261</v>
+        <v>481</v>
       </c>
       <c r="M68" s="10">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="IE68"/>
     </row>
-    <row r="69" spans="3:239" ht="19.5" customHeight="1">
+    <row r="69" spans="3:239" ht="22.5" customHeight="1">
       <c r="C69" s="8">
-        <v>10415</v>
+        <v>10400</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>259</v>
+        <v>98</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>10401</v>
       </c>
       <c r="G69" s="10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H69" s="10">
         <v>0</v>
       </c>
       <c r="I69" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="J69" s="11">
+        <v>100</v>
       </c>
       <c r="K69" s="10"/>
-      <c r="L69" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="L69" s="10"/>
       <c r="M69" s="10">
-        <v>0.04</v>
-      </c>
-      <c r="IE69"/>
+        <v>0.05</v>
+      </c>
     </row>
     <row r="70" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C70" s="8">
-        <v>11100</v>
+        <v>10401</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F70" s="8">
-        <v>11101</v>
+        <v>10402</v>
       </c>
       <c r="G70" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="10">
         <v>0</v>
       </c>
       <c r="I70" s="10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" s="11">
+        <v>220</v>
+      </c>
+      <c r="K70" s="10"/>
+      <c r="L70" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="K70" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="L70" s="10"/>
       <c r="M70" s="10">
         <v>0.05</v>
       </c>
     </row>
     <row r="71" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C71" s="8">
-        <v>11101</v>
+        <v>10402</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F71" s="8">
-        <v>11102</v>
+        <v>10403</v>
       </c>
       <c r="G71" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" s="10">
         <v>0</v>
       </c>
       <c r="I71" s="10">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J71" s="11">
-        <v>220</v>
-      </c>
-      <c r="K71" s="10" t="s">
-        <v>179</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="K71" s="10"/>
       <c r="L71" s="10" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="M71" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="72" spans="3:239" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+      <c r="IE71"/>
+    </row>
+    <row r="72" spans="3:239" ht="19.5" customHeight="1">
       <c r="C72" s="8">
-        <v>11102</v>
+        <v>10403</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="F72" s="8">
-        <v>11103</v>
+        <v>10404</v>
       </c>
       <c r="G72" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" s="10">
         <v>0</v>
       </c>
       <c r="I72" s="10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J72" s="11">
-        <v>375</v>
-      </c>
-      <c r="K72" s="10" t="s">
-        <v>180</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="K72" s="10"/>
       <c r="L72" s="10" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="M72" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="73" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="IE72"/>
+    </row>
+    <row r="73" spans="3:239" ht="19.5" customHeight="1">
       <c r="C73" s="8">
-        <v>11103</v>
+        <v>10404</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="F73" s="8">
-        <v>11104</v>
+        <v>10405</v>
       </c>
       <c r="G73" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="10">
         <v>0</v>
@@ -6390,83 +6660,78 @@
         <v>0.6</v>
       </c>
       <c r="J73" s="11">
-        <v>560</v>
-      </c>
-      <c r="K73" s="10" t="s">
-        <v>181</v>
-      </c>
+        <v>775</v>
+      </c>
+      <c r="K73" s="10"/>
       <c r="L73" s="10" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="M73" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="74" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="IE73"/>
+    </row>
+    <row r="74" spans="3:239" ht="22.5" customHeight="1">
       <c r="C74" s="8">
-        <v>11104</v>
+        <v>10405</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F74" s="8">
-        <v>11105</v>
+        <v>10406</v>
       </c>
       <c r="G74" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H74" s="10">
         <v>0</v>
       </c>
       <c r="I74" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J74" s="11">
-        <v>775</v>
-      </c>
-      <c r="K74" s="10" t="s">
-        <v>182</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="K74" s="10"/>
       <c r="L74" s="10" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="M74" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="75" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C75" s="8">
-        <v>11105</v>
+        <v>10406</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="F75" s="8">
-        <v>11106</v>
+        <v>10407</v>
       </c>
       <c r="G75" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H75" s="10">
         <v>0</v>
       </c>
       <c r="I75" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J75" s="11">
-        <v>1020</v>
-      </c>
-      <c r="K75" s="10" t="s">
-        <v>177</v>
-      </c>
+        <v>1330</v>
+      </c>
+      <c r="K75" s="10"/>
       <c r="L75" s="10" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="M75" s="10">
         <v>0.05</v>
@@ -6474,647 +6739,651 @@
     </row>
     <row r="76" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C76" s="8">
-        <v>11106</v>
+        <v>10407</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="F76" s="8">
-        <v>11107</v>
+        <v>10408</v>
       </c>
       <c r="G76" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H76" s="10">
         <v>0</v>
       </c>
       <c r="I76" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J76" s="11">
+        <v>1680</v>
+      </c>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="M76" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE76"/>
+    </row>
+    <row r="77" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C77" s="8">
+        <v>10408</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="F77" s="8">
+        <v>10409</v>
+      </c>
+      <c r="G77" s="10">
+        <v>8</v>
+      </c>
+      <c r="H77" s="10">
+        <v>0</v>
+      </c>
+      <c r="I77" s="10">
         <v>0.6</v>
       </c>
-      <c r="J76" s="11">
-        <v>1330</v>
-      </c>
-      <c r="K76" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="L76" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="M76" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="77" spans="3:239" ht="20.100000000000001" customHeight="1">
-      <c r="C77" s="8">
-        <v>11107</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="F77" s="8">
-        <v>11108</v>
-      </c>
-      <c r="G77" s="10">
-        <v>7</v>
-      </c>
-      <c r="H77" s="10">
-        <v>0</v>
-      </c>
-      <c r="I77" s="10">
-        <v>0.5</v>
-      </c>
       <c r="J77" s="11">
-        <v>1680</v>
-      </c>
-      <c r="K77" s="10" t="s">
-        <v>184</v>
-      </c>
+        <v>2070</v>
+      </c>
+      <c r="K77" s="10"/>
       <c r="L77" s="10" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="M77" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="78" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="IE77"/>
+    </row>
+    <row r="78" spans="3:239" ht="19.5" customHeight="1">
       <c r="C78" s="8">
-        <v>11108</v>
+        <v>10409</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="F78" s="8">
-        <v>11109</v>
+        <v>10410</v>
       </c>
       <c r="G78" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H78" s="10">
         <v>0</v>
       </c>
       <c r="I78" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J78" s="11">
-        <v>2070</v>
-      </c>
-      <c r="K78" s="10" t="s">
-        <v>185</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="K78" s="10"/>
       <c r="L78" s="10" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="M78" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="79" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="IE78"/>
+    </row>
+    <row r="79" spans="3:239" ht="19.5" customHeight="1">
       <c r="C79" s="8">
-        <v>11109</v>
+        <v>10410</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="F79" s="8">
-        <v>11110</v>
+        <v>10411</v>
       </c>
       <c r="G79" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H79" s="10">
         <v>0</v>
       </c>
       <c r="I79" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="J79" s="11">
-        <v>2500</v>
-      </c>
-      <c r="K79" s="10" t="s">
-        <v>186</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K79" s="10"/>
       <c r="L79" s="10" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="M79" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="80" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="IE79"/>
+    </row>
+    <row r="80" spans="3:239" ht="19.5" customHeight="1">
       <c r="C80" s="8">
-        <v>11110</v>
+        <v>10411</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="F80" s="8">
-        <v>11111</v>
+        <v>10412</v>
       </c>
       <c r="G80" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H80" s="10">
         <v>0</v>
       </c>
       <c r="I80" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="K80" s="10" t="s">
-        <v>187</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="K80" s="10"/>
       <c r="L80" s="10" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="M80" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="IE80"/>
+    </row>
+    <row r="81" spans="3:239" ht="19.5" customHeight="1">
       <c r="C81" s="8">
-        <v>11111</v>
+        <v>10412</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="F81" s="8">
-        <v>11112</v>
+        <v>10413</v>
       </c>
       <c r="G81" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H81" s="10">
         <v>0</v>
       </c>
       <c r="I81" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="K81" s="10" t="s">
-        <v>188</v>
+        <v>264</v>
       </c>
       <c r="L81" s="10" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="M81" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="IE81"/>
+    </row>
+    <row r="82" spans="3:239" ht="19.5" customHeight="1">
       <c r="C82" s="8">
-        <v>11112</v>
+        <v>10413</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="F82" s="8">
-        <v>11113</v>
+        <v>10414</v>
       </c>
       <c r="G82" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H82" s="10">
         <v>0</v>
       </c>
       <c r="I82" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J82" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K82" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L82" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="M82" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="IE82"/>
+    </row>
+    <row r="83" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C83" s="8">
+        <v>10414</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F83" s="8">
+        <v>10415</v>
+      </c>
+      <c r="G83" s="10">
+        <v>14</v>
+      </c>
+      <c r="H83" s="10">
+        <v>0</v>
+      </c>
+      <c r="I83" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J83" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="K82" s="10" t="s">
+      <c r="K83" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="L82" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="M82" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="83" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C83" s="8">
-        <v>11113</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="F83" s="8">
-        <v>11114</v>
-      </c>
-      <c r="G83" s="10">
-        <v>13</v>
-      </c>
-      <c r="H83" s="10">
-        <v>0</v>
-      </c>
-      <c r="I83" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K83" s="10" t="s">
-        <v>267</v>
-      </c>
       <c r="L83" s="10" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="M83" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="IE83"/>
+    </row>
+    <row r="84" spans="3:239" ht="19.5" customHeight="1">
       <c r="C84" s="8">
-        <v>11114</v>
+        <v>10415</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="F84" s="8">
-        <v>11115</v>
+        <v>10416</v>
       </c>
       <c r="G84" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="10">
         <v>0</v>
       </c>
       <c r="I84" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>241</v>
+        <v>425</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>268</v>
+        <v>436</v>
       </c>
       <c r="L84" s="10" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M84" s="10">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="IE84"/>
+    </row>
+    <row r="85" spans="3:239" ht="19.5" customHeight="1">
       <c r="C85" s="8">
-        <v>11115</v>
+        <v>10416</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>265</v>
+        <v>462</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>367</v>
+        <v>467</v>
       </c>
       <c r="F85" s="8">
-        <v>0</v>
+        <v>10417</v>
       </c>
       <c r="G85" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H85" s="10">
         <v>0</v>
       </c>
       <c r="I85" s="10">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K85" s="10">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>437</v>
       </c>
       <c r="L85" s="10" t="s">
-        <v>271</v>
+        <v>472</v>
       </c>
       <c r="M85" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="86" spans="3:13" ht="20.100000000000001" customHeight="1">
+        <v>0.03</v>
+      </c>
+      <c r="IE85"/>
+    </row>
+    <row r="86" spans="3:239" ht="19.5" customHeight="1">
       <c r="C86" s="8">
-        <v>11200</v>
+        <v>10417</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>138</v>
+        <v>463</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>368</v>
+        <v>468</v>
       </c>
       <c r="F86" s="8">
-        <v>11201</v>
+        <v>10418</v>
       </c>
       <c r="G86" s="10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H86" s="10">
         <v>0</v>
       </c>
       <c r="I86" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="L86" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="M86" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="IE86"/>
+    </row>
+    <row r="87" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C87" s="8">
+        <v>10418</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="F87" s="8">
+        <v>10419</v>
+      </c>
+      <c r="G87" s="10">
+        <v>18</v>
+      </c>
+      <c r="H87" s="10">
+        <v>0</v>
+      </c>
+      <c r="I87" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="M87" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="IE87"/>
+    </row>
+    <row r="88" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C88" s="8">
+        <v>10419</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="F88" s="8">
+        <v>10420</v>
+      </c>
+      <c r="G88" s="10">
+        <v>19</v>
+      </c>
+      <c r="H88" s="10">
+        <v>0</v>
+      </c>
+      <c r="I88" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="L88" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="M88" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="IE88"/>
+    </row>
+    <row r="89" spans="3:239" ht="19.5" customHeight="1">
+      <c r="C89" s="8">
+        <v>10420</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F89" s="8">
+        <v>0</v>
+      </c>
+      <c r="G89" s="10">
+        <v>20</v>
+      </c>
+      <c r="H89" s="10">
+        <v>0</v>
+      </c>
+      <c r="I89" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="K89" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="M89" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="IE89"/>
+    </row>
+    <row r="90" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="C90" s="8">
+        <v>11100</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F90" s="8">
+        <v>11101</v>
+      </c>
+      <c r="G90" s="10">
+        <v>0</v>
+      </c>
+      <c r="H90" s="10">
+        <v>0</v>
+      </c>
+      <c r="I90" s="10">
         <v>1</v>
       </c>
-      <c r="J86" s="11">
+      <c r="J90" s="11">
         <v>100</v>
       </c>
-      <c r="K86" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="L86" s="10"/>
-      <c r="M86" s="10">
+      <c r="K90" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="L90" s="10"/>
+      <c r="M90" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C87" s="8">
-        <v>11201</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="F87" s="8">
-        <v>11202</v>
-      </c>
-      <c r="G87" s="10">
+    <row r="91" spans="3:239" ht="20.100000000000001" customHeight="1">
+      <c r="C91" s="8">
+        <v>11101</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="F91" s="8">
+        <v>11102</v>
+      </c>
+      <c r="G91" s="10">
         <v>1</v>
       </c>
-      <c r="H87" s="10">
-        <v>0</v>
-      </c>
-      <c r="I87" s="10">
+      <c r="H91" s="10">
+        <v>0</v>
+      </c>
+      <c r="I91" s="10">
         <v>0.8</v>
       </c>
-      <c r="J87" s="11">
+      <c r="J91" s="11">
         <v>220</v>
-      </c>
-      <c r="K87" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="M87" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="88" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C88" s="8">
-        <v>11202</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E88" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="F88" s="8">
-        <v>11203</v>
-      </c>
-      <c r="G88" s="10">
-        <v>2</v>
-      </c>
-      <c r="H88" s="10">
-        <v>0</v>
-      </c>
-      <c r="I88" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J88" s="11">
-        <v>375</v>
-      </c>
-      <c r="K88" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="L88" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="M88" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="89" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C89" s="8">
-        <v>11203</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E89" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="F89" s="8">
-        <v>11204</v>
-      </c>
-      <c r="G89" s="10">
-        <v>3</v>
-      </c>
-      <c r="H89" s="10">
-        <v>0</v>
-      </c>
-      <c r="I89" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J89" s="11">
-        <v>560</v>
-      </c>
-      <c r="K89" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="L89" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="M89" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="90" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C90" s="8">
-        <v>11204</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="F90" s="8">
-        <v>11205</v>
-      </c>
-      <c r="G90" s="10">
-        <v>4</v>
-      </c>
-      <c r="H90" s="10">
-        <v>0</v>
-      </c>
-      <c r="I90" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J90" s="11">
-        <v>775</v>
-      </c>
-      <c r="K90" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="L90" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="M90" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="91" spans="3:13" ht="20.100000000000001" customHeight="1">
-      <c r="C91" s="8">
-        <v>11205</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="F91" s="8">
-        <v>11206</v>
-      </c>
-      <c r="G91" s="10">
-        <v>5</v>
-      </c>
-      <c r="H91" s="10">
-        <v>0</v>
-      </c>
-      <c r="I91" s="10">
-        <v>1</v>
-      </c>
-      <c r="J91" s="11">
-        <v>1020</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>177</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="M91" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="92" spans="3:13" ht="20.100000000000001" customHeight="1">
+    <row r="92" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C92" s="8">
-        <v>11206</v>
+        <v>11102</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="F92" s="8">
-        <v>11207</v>
+        <v>11103</v>
       </c>
       <c r="G92" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H92" s="10">
         <v>0</v>
       </c>
       <c r="I92" s="10">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J92" s="11">
-        <v>1330</v>
+        <v>375</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="M92" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="93" spans="3:13" ht="20.100000000000001" customHeight="1">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="93" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C93" s="8">
-        <v>11207</v>
+        <v>11103</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="F93" s="8">
-        <v>11208</v>
+        <v>11104</v>
       </c>
       <c r="G93" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H93" s="10">
         <v>0</v>
       </c>
       <c r="I93" s="10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J93" s="11">
-        <v>1680</v>
+        <v>560</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="M93" s="10">
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="3:13" ht="20.100000000000001" customHeight="1">
+    <row r="94" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C94" s="8">
-        <v>11208</v>
+        <v>11104</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="F94" s="8">
-        <v>11209</v>
+        <v>11105</v>
       </c>
       <c r="G94" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H94" s="10">
         <v>0</v>
@@ -7123,33 +7392,33 @@
         <v>0.6</v>
       </c>
       <c r="J94" s="11">
-        <v>2070</v>
+        <v>775</v>
       </c>
       <c r="K94" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L94" s="10" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="M94" s="10">
         <v>0.04</v>
       </c>
     </row>
-    <row r="95" spans="3:13" ht="20.100000000000001" customHeight="1">
+    <row r="95" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C95" s="8">
-        <v>11209</v>
+        <v>11105</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="F95" s="8">
-        <v>11210</v>
+        <v>11106</v>
       </c>
       <c r="G95" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H95" s="10">
         <v>0</v>
@@ -7158,33 +7427,33 @@
         <v>0.6</v>
       </c>
       <c r="J95" s="11">
-        <v>2500</v>
+        <v>1020</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L95" s="10" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="M95" s="10">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="96" spans="3:13" ht="20.100000000000001" customHeight="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="96" spans="3:239" ht="20.100000000000001" customHeight="1">
       <c r="C96" s="8">
-        <v>11210</v>
+        <v>11106</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="F96" s="8">
-        <v>11211</v>
+        <v>11107</v>
       </c>
       <c r="G96" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H96" s="10">
         <v>0</v>
@@ -7192,14 +7461,14 @@
       <c r="I96" s="10">
         <v>0.6</v>
       </c>
-      <c r="J96" s="11" t="s">
-        <v>42</v>
+      <c r="J96" s="11">
+        <v>1330</v>
       </c>
       <c r="K96" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L96" s="10" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="M96" s="10">
         <v>0.04</v>
@@ -7207,34 +7476,34 @@
     </row>
     <row r="97" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C97" s="8">
-        <v>11211</v>
+        <v>11107</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="F97" s="8">
-        <v>11212</v>
+        <v>11108</v>
       </c>
       <c r="G97" s="10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H97" s="10">
         <v>0</v>
       </c>
       <c r="I97" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>45</v>
+        <v>0.5</v>
+      </c>
+      <c r="J97" s="11">
+        <v>1680</v>
       </c>
       <c r="K97" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L97" s="10" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="M97" s="10">
         <v>0.04</v>
@@ -7242,34 +7511,34 @@
     </row>
     <row r="98" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C98" s="8">
-        <v>11212</v>
+        <v>11108</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="F98" s="8">
-        <v>11213</v>
+        <v>11109</v>
       </c>
       <c r="G98" s="10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H98" s="10">
         <v>0</v>
       </c>
       <c r="I98" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>239</v>
+        <v>0.5</v>
+      </c>
+      <c r="J98" s="11">
+        <v>2070</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="L98" s="10" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="M98" s="10">
         <v>0.04</v>
@@ -7277,34 +7546,34 @@
     </row>
     <row r="99" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C99" s="8">
-        <v>11213</v>
+        <v>11109</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>272</v>
+        <v>132</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="F99" s="8">
-        <v>11214</v>
+        <v>11110</v>
       </c>
       <c r="G99" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H99" s="10">
         <v>0</v>
       </c>
       <c r="I99" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>240</v>
+        <v>0.5</v>
+      </c>
+      <c r="J99" s="11">
+        <v>2500</v>
       </c>
       <c r="K99" s="10" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="L99" s="10" t="s">
-        <v>275</v>
+        <v>195</v>
       </c>
       <c r="M99" s="10">
         <v>0.04</v>
@@ -7312,34 +7581,34 @@
     </row>
     <row r="100" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C100" s="8">
-        <v>11214</v>
+        <v>11110</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="F100" s="8">
-        <v>11215</v>
+        <v>11111</v>
       </c>
       <c r="G100" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H100" s="10">
         <v>0</v>
       </c>
       <c r="I100" s="10">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J100" s="11" t="s">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="L100" s="10" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="M100" s="10">
         <v>0.04</v>
@@ -7347,34 +7616,34 @@
     </row>
     <row r="101" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C101" s="8">
-        <v>11215</v>
+        <v>11111</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="F101" s="8">
-        <v>0</v>
+        <v>11112</v>
       </c>
       <c r="G101" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H101" s="10">
         <v>0</v>
       </c>
       <c r="I101" s="10">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J101" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K101" s="10">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L101" s="10" t="s">
-        <v>277</v>
+        <v>197</v>
       </c>
       <c r="M101" s="10">
         <v>0.04</v>
@@ -7382,102 +7651,104 @@
     </row>
     <row r="102" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C102" s="8">
-        <v>11300</v>
+        <v>11112</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="F102" s="8">
-        <v>11301</v>
+        <v>11113</v>
       </c>
       <c r="G102" s="10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H102" s="10">
         <v>0</v>
       </c>
       <c r="I102" s="10">
-        <v>1</v>
-      </c>
-      <c r="J102" s="11">
-        <v>100</v>
+        <v>0.5</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="K102" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="L102" s="10"/>
+        <v>264</v>
+      </c>
+      <c r="L102" s="10" t="s">
+        <v>198</v>
+      </c>
       <c r="M102" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="103" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C103" s="8">
-        <v>11301</v>
+        <v>11113</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="F103" s="8">
-        <v>11302</v>
+        <v>11114</v>
       </c>
       <c r="G103" s="10">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H103" s="10">
         <v>0</v>
       </c>
       <c r="I103" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J103" s="11">
-        <v>220</v>
+        <v>0.5</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="L103" s="10" t="s">
-        <v>213</v>
+        <v>267</v>
       </c>
       <c r="M103" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="104" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C104" s="8">
-        <v>11302</v>
+        <v>11114</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>153</v>
+        <v>262</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F104" s="8">
-        <v>11303</v>
+        <v>11115</v>
       </c>
       <c r="G104" s="10">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H104" s="10">
         <v>0</v>
       </c>
       <c r="I104" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J104" s="11">
-        <v>375</v>
+        <v>0.5</v>
+      </c>
+      <c r="J104" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="K104" s="10" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="L104" s="10" t="s">
-        <v>214</v>
+        <v>268</v>
       </c>
       <c r="M104" s="10">
         <v>0.04</v>
@@ -7485,34 +7756,34 @@
     </row>
     <row r="105" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C105" s="8">
-        <v>11303</v>
+        <v>11115</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>154</v>
+        <v>263</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="F105" s="8">
-        <v>11304</v>
+        <v>0</v>
       </c>
       <c r="G105" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H105" s="10">
         <v>0</v>
       </c>
       <c r="I105" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J105" s="11">
-        <v>560</v>
-      </c>
-      <c r="K105" s="10" t="s">
-        <v>181</v>
+        <v>0.5</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K105" s="10">
+        <v>0</v>
       </c>
       <c r="L105" s="10" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="M105" s="10">
         <v>0.04</v>
@@ -7520,54 +7791,52 @@
     </row>
     <row r="106" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C106" s="8">
-        <v>11304</v>
+        <v>11200</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="F106" s="8">
-        <v>11305</v>
+        <v>11201</v>
       </c>
       <c r="G106" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H106" s="10">
         <v>0</v>
       </c>
       <c r="I106" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J106" s="11">
-        <v>775</v>
+        <v>100</v>
       </c>
       <c r="K106" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="L106" s="10" t="s">
-        <v>216</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="L106" s="10"/>
       <c r="M106" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="107" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C107" s="8">
-        <v>11305</v>
+        <v>11201</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="F107" s="8">
-        <v>11306</v>
+        <v>11202</v>
       </c>
       <c r="G107" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H107" s="10">
         <v>0</v>
@@ -7576,13 +7845,13 @@
         <v>0.8</v>
       </c>
       <c r="J107" s="11">
-        <v>1020</v>
+        <v>220</v>
       </c>
       <c r="K107" s="10" t="s">
         <v>177</v>
       </c>
       <c r="L107" s="10" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="M107" s="10">
         <v>0.05</v>
@@ -7590,19 +7859,19 @@
     </row>
     <row r="108" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C108" s="8">
-        <v>11306</v>
+        <v>11202</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="F108" s="8">
-        <v>11307</v>
+        <v>11203</v>
       </c>
       <c r="G108" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H108" s="10">
         <v>0</v>
@@ -7611,13 +7880,13 @@
         <v>0.7</v>
       </c>
       <c r="J108" s="11">
-        <v>1330</v>
+        <v>375</v>
       </c>
       <c r="K108" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L108" s="10" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="M108" s="10">
         <v>0.04</v>
@@ -7625,19 +7894,19 @@
     </row>
     <row r="109" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C109" s="8">
-        <v>11307</v>
+        <v>11203</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="F109" s="8">
-        <v>11308</v>
+        <v>11204</v>
       </c>
       <c r="G109" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H109" s="10">
         <v>0</v>
@@ -7646,13 +7915,13 @@
         <v>0.6</v>
       </c>
       <c r="J109" s="11">
-        <v>1680</v>
+        <v>560</v>
       </c>
       <c r="K109" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="L109" s="10" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="M109" s="10">
         <v>0.04</v>
@@ -7660,19 +7929,19 @@
     </row>
     <row r="110" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C110" s="8">
-        <v>11308</v>
+        <v>11204</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="F110" s="8">
-        <v>11309</v>
+        <v>11205</v>
       </c>
       <c r="G110" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H110" s="10">
         <v>0</v>
@@ -7681,13 +7950,13 @@
         <v>0.6</v>
       </c>
       <c r="J110" s="11">
-        <v>2070</v>
+        <v>775</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L110" s="10" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="M110" s="10">
         <v>0.04</v>
@@ -7695,104 +7964,104 @@
     </row>
     <row r="111" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C111" s="8">
-        <v>11309</v>
+        <v>11205</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="F111" s="8">
-        <v>11310</v>
+        <v>11206</v>
       </c>
       <c r="G111" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H111" s="10">
         <v>0</v>
       </c>
       <c r="I111" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J111" s="11">
-        <v>2500</v>
+        <v>1020</v>
       </c>
       <c r="K111" s="10" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L111" s="10" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="M111" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="112" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C112" s="8">
-        <v>11310</v>
+        <v>11206</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="F112" s="8">
-        <v>11311</v>
+        <v>11207</v>
       </c>
       <c r="G112" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H112" s="10">
         <v>0</v>
       </c>
       <c r="I112" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J112" s="11" t="s">
-        <v>42</v>
+        <v>0.8</v>
+      </c>
+      <c r="J112" s="11">
+        <v>1330</v>
       </c>
       <c r="K112" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L112" s="10" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="M112" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="113" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C113" s="8">
-        <v>11311</v>
+        <v>11207</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="F113" s="8">
-        <v>11312</v>
+        <v>11208</v>
       </c>
       <c r="G113" s="10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H113" s="10">
         <v>0</v>
       </c>
       <c r="I113" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J113" s="11" t="s">
-        <v>45</v>
+        <v>0.7</v>
+      </c>
+      <c r="J113" s="11">
+        <v>1680</v>
       </c>
       <c r="K113" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L113" s="10" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="M113" s="10">
         <v>0.04</v>
@@ -7800,19 +8069,19 @@
     </row>
     <row r="114" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C114" s="8">
-        <v>11312</v>
+        <v>11208</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="F114" s="8">
-        <v>11313</v>
+        <v>11209</v>
       </c>
       <c r="G114" s="10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H114" s="10">
         <v>0</v>
@@ -7820,14 +8089,14 @@
       <c r="I114" s="10">
         <v>0.6</v>
       </c>
-      <c r="J114" s="11" t="s">
-        <v>239</v>
+      <c r="J114" s="11">
+        <v>2070</v>
       </c>
       <c r="K114" s="10" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="L114" s="10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="M114" s="10">
         <v>0.04</v>
@@ -7835,19 +8104,19 @@
     </row>
     <row r="115" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C115" s="8">
-        <v>11313</v>
+        <v>11209</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>278</v>
+        <v>145</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="F115" s="8">
-        <v>11314</v>
+        <v>11210</v>
       </c>
       <c r="G115" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H115" s="10">
         <v>0</v>
@@ -7855,14 +8124,14 @@
       <c r="I115" s="10">
         <v>0.6</v>
       </c>
-      <c r="J115" s="11" t="s">
-        <v>240</v>
+      <c r="J115" s="11">
+        <v>2500</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="L115" s="10" t="s">
-        <v>275</v>
+        <v>207</v>
       </c>
       <c r="M115" s="10">
         <v>0.04</v>
@@ -7870,19 +8139,19 @@
     </row>
     <row r="116" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C116" s="8">
-        <v>11314</v>
+        <v>11210</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>279</v>
+        <v>146</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="F116" s="8">
-        <v>11315</v>
+        <v>11211</v>
       </c>
       <c r="G116" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H116" s="10">
         <v>0</v>
@@ -7891,13 +8160,13 @@
         <v>0.6</v>
       </c>
       <c r="J116" s="11" t="s">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="K116" s="10" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="L116" s="10" t="s">
-        <v>276</v>
+        <v>208</v>
       </c>
       <c r="M116" s="10">
         <v>0.04</v>
@@ -7905,19 +8174,19 @@
     </row>
     <row r="117" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C117" s="8">
-        <v>11315</v>
+        <v>11211</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>280</v>
+        <v>147</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="F117" s="8">
-        <v>0</v>
+        <v>11212</v>
       </c>
       <c r="G117" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H117" s="10">
         <v>0</v>
@@ -7926,13 +8195,13 @@
         <v>0.6</v>
       </c>
       <c r="J117" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K117" s="10">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="K117" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="L117" s="10" t="s">
-        <v>277</v>
+        <v>209</v>
       </c>
       <c r="M117" s="10">
         <v>0.04</v>
@@ -7940,102 +8209,104 @@
     </row>
     <row r="118" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C118" s="8">
-        <v>11400</v>
+        <v>11212</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="F118" s="8">
-        <v>11401</v>
+        <v>11213</v>
       </c>
       <c r="G118" s="10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H118" s="10">
         <v>0</v>
       </c>
       <c r="I118" s="10">
-        <v>1</v>
-      </c>
-      <c r="J118" s="11">
-        <v>100</v>
+        <v>0.6</v>
+      </c>
+      <c r="J118" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="L118" s="10"/>
+        <v>264</v>
+      </c>
+      <c r="L118" s="10" t="s">
+        <v>210</v>
+      </c>
       <c r="M118" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="119" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C119" s="8">
-        <v>11401</v>
+        <v>11213</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="F119" s="8">
-        <v>11402</v>
+        <v>11214</v>
       </c>
       <c r="G119" s="10">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H119" s="10">
         <v>0</v>
       </c>
       <c r="I119" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="J119" s="11">
-        <v>220</v>
+        <v>0.6</v>
+      </c>
+      <c r="J119" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="L119" s="10" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="M119" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="120" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C120" s="8">
-        <v>11402</v>
+        <v>11214</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="F120" s="8">
-        <v>11403</v>
+        <v>11215</v>
       </c>
       <c r="G120" s="10">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H120" s="10">
         <v>0</v>
       </c>
       <c r="I120" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="J120" s="11">
-        <v>375</v>
+        <v>0.6</v>
+      </c>
+      <c r="J120" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="K120" s="10" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="L120" s="10" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="M120" s="10">
         <v>0.04</v>
@@ -8043,19 +8314,19 @@
     </row>
     <row r="121" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C121" s="8">
-        <v>11403</v>
+        <v>11215</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="F121" s="8">
-        <v>11404</v>
+        <v>0</v>
       </c>
       <c r="G121" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H121" s="10">
         <v>0</v>
@@ -8063,14 +8334,14 @@
       <c r="I121" s="10">
         <v>0.6</v>
       </c>
-      <c r="J121" s="11">
-        <v>560</v>
-      </c>
-      <c r="K121" s="10" t="s">
-        <v>181</v>
+      <c r="J121" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K121" s="10">
+        <v>0</v>
       </c>
       <c r="L121" s="10" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="M121" s="10">
         <v>0.04</v>
@@ -8078,69 +8349,67 @@
     </row>
     <row r="122" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C122" s="8">
-        <v>11404</v>
+        <v>11300</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="F122" s="8">
-        <v>11405</v>
+        <v>11301</v>
       </c>
       <c r="G122" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H122" s="10">
         <v>0</v>
       </c>
       <c r="I122" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J122" s="11">
-        <v>775</v>
+        <v>100</v>
       </c>
       <c r="K122" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="L122" s="10" t="s">
-        <v>227</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="L122" s="10"/>
       <c r="M122" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="123" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C123" s="8">
-        <v>11405</v>
+        <v>11301</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F123" s="8">
-        <v>11406</v>
+        <v>11302</v>
       </c>
       <c r="G123" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H123" s="10">
         <v>0</v>
       </c>
       <c r="I123" s="10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J123" s="11">
-        <v>1020</v>
+        <v>220</v>
       </c>
       <c r="K123" s="10" t="s">
         <v>177</v>
       </c>
       <c r="L123" s="10" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="M123" s="10">
         <v>0.05</v>
@@ -8148,69 +8417,69 @@
     </row>
     <row r="124" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C124" s="8">
-        <v>11406</v>
+        <v>11302</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E124" s="12" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="F124" s="8">
-        <v>11407</v>
+        <v>11303</v>
       </c>
       <c r="G124" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H124" s="10">
         <v>0</v>
       </c>
       <c r="I124" s="10">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J124" s="11">
-        <v>1330</v>
+        <v>375</v>
       </c>
       <c r="K124" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L124" s="10" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="M124" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="125" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C125" s="8">
-        <v>11407</v>
+        <v>11303</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="F125" s="8">
-        <v>11408</v>
+        <v>11304</v>
       </c>
       <c r="G125" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H125" s="10">
         <v>0</v>
       </c>
       <c r="I125" s="10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J125" s="11">
-        <v>1680</v>
+        <v>560</v>
       </c>
       <c r="K125" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="L125" s="10" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="M125" s="10">
         <v>0.04</v>
@@ -8218,19 +8487,19 @@
     </row>
     <row r="126" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C126" s="8">
-        <v>11408</v>
+        <v>11304</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="F126" s="8">
-        <v>11409</v>
+        <v>11305</v>
       </c>
       <c r="G126" s="10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H126" s="10">
         <v>0</v>
@@ -8239,13 +8508,13 @@
         <v>0.6</v>
       </c>
       <c r="J126" s="11">
-        <v>2070</v>
+        <v>775</v>
       </c>
       <c r="K126" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L126" s="10" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="M126" s="10">
         <v>0.04</v>
@@ -8253,69 +8522,69 @@
     </row>
     <row r="127" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C127" s="8">
-        <v>11409</v>
+        <v>11305</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E127" s="12" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
       <c r="F127" s="8">
-        <v>11410</v>
+        <v>11306</v>
       </c>
       <c r="G127" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H127" s="10">
         <v>0</v>
       </c>
       <c r="I127" s="10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J127" s="11">
-        <v>2500</v>
+        <v>1020</v>
       </c>
       <c r="K127" s="10" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="M127" s="10">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="128" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C128" s="8">
-        <v>11410</v>
+        <v>11306</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="E128" s="12" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="F128" s="8">
-        <v>11411</v>
+        <v>11307</v>
       </c>
       <c r="G128" s="10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H128" s="10">
         <v>0</v>
       </c>
       <c r="I128" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>42</v>
+        <v>0.7</v>
+      </c>
+      <c r="J128" s="11">
+        <v>1330</v>
       </c>
       <c r="K128" s="10" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L128" s="10" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="M128" s="10">
         <v>0.04</v>
@@ -8323,19 +8592,19 @@
     </row>
     <row r="129" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C129" s="8">
-        <v>11411</v>
+        <v>11307</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="F129" s="8">
-        <v>11412</v>
+        <v>11308</v>
       </c>
       <c r="G129" s="10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H129" s="10">
         <v>0</v>
@@ -8343,14 +8612,14 @@
       <c r="I129" s="10">
         <v>0.6</v>
       </c>
-      <c r="J129" s="11" t="s">
-        <v>45</v>
+      <c r="J129" s="11">
+        <v>1680</v>
       </c>
       <c r="K129" s="10" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L129" s="10" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="M129" s="10">
         <v>0.04</v>
@@ -8358,19 +8627,19 @@
     </row>
     <row r="130" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C130" s="8">
-        <v>11412</v>
+        <v>11308</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="F130" s="8">
-        <v>11413</v>
+        <v>11309</v>
       </c>
       <c r="G130" s="10">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H130" s="10">
         <v>0</v>
@@ -8378,14 +8647,14 @@
       <c r="I130" s="10">
         <v>0.6</v>
       </c>
-      <c r="J130" s="11" t="s">
-        <v>239</v>
+      <c r="J130" s="11">
+        <v>2070</v>
       </c>
       <c r="K130" s="10" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="L130" s="10" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="M130" s="10">
         <v>0.04</v>
@@ -8393,19 +8662,19 @@
     </row>
     <row r="131" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C131" s="8">
-        <v>11413</v>
+        <v>11309</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>281</v>
+        <v>158</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="F131" s="8">
-        <v>11414</v>
+        <v>11310</v>
       </c>
       <c r="G131" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H131" s="10">
         <v>0</v>
@@ -8413,14 +8682,14 @@
       <c r="I131" s="10">
         <v>0.6</v>
       </c>
-      <c r="J131" s="11" t="s">
-        <v>240</v>
+      <c r="J131" s="11">
+        <v>2500</v>
       </c>
       <c r="K131" s="10" t="s">
-        <v>267</v>
+        <v>184</v>
       </c>
       <c r="L131" s="10" t="s">
-        <v>284</v>
+        <v>219</v>
       </c>
       <c r="M131" s="10">
         <v>0.04</v>
@@ -8428,19 +8697,19 @@
     </row>
     <row r="132" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C132" s="8">
-        <v>11414</v>
+        <v>11310</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>282</v>
+        <v>159</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="F132" s="8">
-        <v>11415</v>
+        <v>11311</v>
       </c>
       <c r="G132" s="10">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H132" s="10">
         <v>0</v>
@@ -8449,13 +8718,13 @@
         <v>0.6</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="K132" s="10" t="s">
-        <v>268</v>
+        <v>185</v>
       </c>
       <c r="L132" s="10" t="s">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="M132" s="10">
         <v>0.04</v>
@@ -8463,19 +8732,19 @@
     </row>
     <row r="133" spans="3:13" ht="20.100000000000001" customHeight="1">
       <c r="C133" s="8">
-        <v>11415</v>
+        <v>11311</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>283</v>
+        <v>160</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="F133" s="8">
-        <v>0</v>
+        <v>11312</v>
       </c>
       <c r="G133" s="10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H133" s="10">
         <v>0</v>
@@ -8484,15 +8753,713 @@
         <v>0.6</v>
       </c>
       <c r="J133" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K133" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L133" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="M133" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="134" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C134" s="8">
+        <v>11312</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="F134" s="8">
+        <v>11313</v>
+      </c>
+      <c r="G134" s="10">
+        <v>12</v>
+      </c>
+      <c r="H134" s="10">
+        <v>0</v>
+      </c>
+      <c r="I134" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="K134" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="L134" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="M134" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="135" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C135" s="8">
+        <v>11313</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="F135" s="8">
+        <v>11314</v>
+      </c>
+      <c r="G135" s="10">
+        <v>13</v>
+      </c>
+      <c r="H135" s="10">
+        <v>0</v>
+      </c>
+      <c r="I135" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J135" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K135" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L135" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="M135" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="136" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C136" s="8">
+        <v>11314</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="F136" s="8">
+        <v>11315</v>
+      </c>
+      <c r="G136" s="10">
+        <v>14</v>
+      </c>
+      <c r="H136" s="10">
+        <v>0</v>
+      </c>
+      <c r="I136" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J136" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K136" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="M136" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="137" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C137" s="8">
+        <v>11315</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="F137" s="8">
+        <v>0</v>
+      </c>
+      <c r="G137" s="10">
+        <v>15</v>
+      </c>
+      <c r="H137" s="10">
+        <v>0</v>
+      </c>
+      <c r="I137" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J137" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K133" s="10">
-        <v>0</v>
-      </c>
-      <c r="L133" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="M133" s="10">
+      <c r="K137" s="10">
+        <v>0</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="M137" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="138" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C138" s="8">
+        <v>11400</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="F138" s="8">
+        <v>11401</v>
+      </c>
+      <c r="G138" s="10">
+        <v>0</v>
+      </c>
+      <c r="H138" s="10">
+        <v>0</v>
+      </c>
+      <c r="I138" s="10">
+        <v>1</v>
+      </c>
+      <c r="J138" s="11">
+        <v>100</v>
+      </c>
+      <c r="K138" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="L138" s="10"/>
+      <c r="M138" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="139" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C139" s="8">
+        <v>11401</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="F139" s="8">
+        <v>11402</v>
+      </c>
+      <c r="G139" s="10">
+        <v>1</v>
+      </c>
+      <c r="H139" s="10">
+        <v>0</v>
+      </c>
+      <c r="I139" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="J139" s="11">
+        <v>220</v>
+      </c>
+      <c r="K139" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="L139" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="M139" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="140" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C140" s="8">
+        <v>11402</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F140" s="8">
+        <v>11403</v>
+      </c>
+      <c r="G140" s="10">
+        <v>2</v>
+      </c>
+      <c r="H140" s="10">
+        <v>0</v>
+      </c>
+      <c r="I140" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J140" s="11">
+        <v>375</v>
+      </c>
+      <c r="K140" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L140" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="M140" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="141" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C141" s="8">
+        <v>11403</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="F141" s="8">
+        <v>11404</v>
+      </c>
+      <c r="G141" s="10">
+        <v>3</v>
+      </c>
+      <c r="H141" s="10">
+        <v>0</v>
+      </c>
+      <c r="I141" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J141" s="11">
+        <v>560</v>
+      </c>
+      <c r="K141" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="L141" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="M141" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="142" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C142" s="8">
+        <v>11404</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="F142" s="8">
+        <v>11405</v>
+      </c>
+      <c r="G142" s="10">
+        <v>4</v>
+      </c>
+      <c r="H142" s="10">
+        <v>0</v>
+      </c>
+      <c r="I142" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J142" s="11">
+        <v>775</v>
+      </c>
+      <c r="K142" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="L142" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="M142" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="143" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C143" s="8">
+        <v>11405</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F143" s="8">
+        <v>11406</v>
+      </c>
+      <c r="G143" s="10">
+        <v>5</v>
+      </c>
+      <c r="H143" s="10">
+        <v>0</v>
+      </c>
+      <c r="I143" s="10">
+        <v>1</v>
+      </c>
+      <c r="J143" s="11">
+        <v>1020</v>
+      </c>
+      <c r="K143" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="M143" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="144" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C144" s="8">
+        <v>11406</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="F144" s="8">
+        <v>11407</v>
+      </c>
+      <c r="G144" s="10">
+        <v>6</v>
+      </c>
+      <c r="H144" s="10">
+        <v>0</v>
+      </c>
+      <c r="I144" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="J144" s="11">
+        <v>1330</v>
+      </c>
+      <c r="K144" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L144" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="M144" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="145" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C145" s="8">
+        <v>11407</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="F145" s="8">
+        <v>11408</v>
+      </c>
+      <c r="G145" s="10">
+        <v>7</v>
+      </c>
+      <c r="H145" s="10">
+        <v>0</v>
+      </c>
+      <c r="I145" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="J145" s="11">
+        <v>1680</v>
+      </c>
+      <c r="K145" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="L145" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="M145" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="146" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C146" s="8">
+        <v>11408</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="F146" s="8">
+        <v>11409</v>
+      </c>
+      <c r="G146" s="10">
+        <v>8</v>
+      </c>
+      <c r="H146" s="10">
+        <v>0</v>
+      </c>
+      <c r="I146" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J146" s="11">
+        <v>2070</v>
+      </c>
+      <c r="K146" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="L146" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="M146" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="147" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C147" s="8">
+        <v>11409</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="F147" s="8">
+        <v>11410</v>
+      </c>
+      <c r="G147" s="10">
+        <v>9</v>
+      </c>
+      <c r="H147" s="10">
+        <v>0</v>
+      </c>
+      <c r="I147" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J147" s="11">
+        <v>2500</v>
+      </c>
+      <c r="K147" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="L147" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="M147" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="148" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C148" s="8">
+        <v>11410</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="F148" s="8">
+        <v>11411</v>
+      </c>
+      <c r="G148" s="10">
+        <v>10</v>
+      </c>
+      <c r="H148" s="10">
+        <v>0</v>
+      </c>
+      <c r="I148" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J148" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K148" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="L148" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="M148" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="149" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C149" s="8">
+        <v>11411</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F149" s="8">
+        <v>11412</v>
+      </c>
+      <c r="G149" s="10">
+        <v>11</v>
+      </c>
+      <c r="H149" s="10">
+        <v>0</v>
+      </c>
+      <c r="I149" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J149" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K149" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L149" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="M149" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="150" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C150" s="8">
+        <v>11412</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="F150" s="8">
+        <v>11413</v>
+      </c>
+      <c r="G150" s="10">
+        <v>12</v>
+      </c>
+      <c r="H150" s="10">
+        <v>0</v>
+      </c>
+      <c r="I150" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J150" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="K150" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="L150" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="M150" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="151" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C151" s="8">
+        <v>11413</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F151" s="8">
+        <v>11414</v>
+      </c>
+      <c r="G151" s="10">
+        <v>13</v>
+      </c>
+      <c r="H151" s="10">
+        <v>0</v>
+      </c>
+      <c r="I151" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K151" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="L151" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="M151" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="152" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C152" s="8">
+        <v>11414</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="F152" s="8">
+        <v>11415</v>
+      </c>
+      <c r="G152" s="10">
+        <v>14</v>
+      </c>
+      <c r="H152" s="10">
+        <v>0</v>
+      </c>
+      <c r="I152" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="K152" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="L152" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="M152" s="10">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="153" spans="3:13" ht="20.100000000000001" customHeight="1">
+      <c r="C153" s="8">
+        <v>11415</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="F153" s="8">
+        <v>0</v>
+      </c>
+      <c r="G153" s="10">
+        <v>15</v>
+      </c>
+      <c r="H153" s="10">
+        <v>0</v>
+      </c>
+      <c r="I153" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J153" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K153" s="10">
+        <v>0</v>
+      </c>
+      <c r="L153" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="M153" s="10">
         <v>0.04</v>
       </c>
     </row>
